--- a/ok-fc_occupancy_pace_150day.xlsx
+++ b/ok-fc_occupancy_pace_150day.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D154"/>
+  <dimension ref="A1:D175"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,35 +415,35 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>05/01</v>
+        <v>05/11</v>
       </c>
       <c r="B2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>936.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>05/02</v>
+        <v>05/12</v>
       </c>
       <c r="B3">
-        <v>25</v>
+        <v>8.33</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>893.7</v>
+        <v>203.15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>05/03</v>
+        <v>05/13</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -457,21 +457,21 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>05/04</v>
+        <v>05/14</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>05/05</v>
+        <v>05/15</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -485,133 +485,133 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>05/06</v>
+        <v>05/16</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>568.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>05/07</v>
+        <v>05/17</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>454.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>05/08</v>
+        <v>05/18</v>
       </c>
       <c r="B9">
-        <v>50</v>
+        <v>8.33</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>2044</v>
+        <v>215.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>05/09</v>
+        <v>05/19</v>
       </c>
       <c r="B10">
-        <v>50</v>
+        <v>16.67</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>2047</v>
+        <v>454.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>05/10</v>
+        <v>05/20</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>05/11</v>
+        <v>05/21</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>394.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>05/12</v>
+        <v>05/22</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>58.33</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>2107.45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>05/13</v>
+        <v>05/23</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>66.67</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>2456.5499999999997</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>05/14</v>
+        <v>05/24</v>
       </c>
       <c r="B15">
-        <v>8.33</v>
+        <v>66.67</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D15">
-        <v>239</v>
+        <v>2783.45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>05/15</v>
+        <v>05/25</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -625,35 +625,35 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>05/16</v>
+        <v>05/26</v>
       </c>
       <c r="B17">
-        <v>16.67</v>
+        <v>50</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>568.8</v>
+        <v>1395.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>05/17</v>
+        <v>05/27</v>
       </c>
       <c r="B18">
-        <v>16.67</v>
+        <v>25</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18">
-        <v>454.1</v>
+        <v>659.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>05/18</v>
+        <v>05/28</v>
       </c>
       <c r="B19">
         <v>8.33</v>
@@ -662,40 +662,40 @@
         <v>1</v>
       </c>
       <c r="D19">
-        <v>215.1</v>
+        <v>199</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>05/19</v>
+        <v>05/29</v>
       </c>
       <c r="B20">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>454.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>05/20</v>
+        <v>05/30</v>
       </c>
       <c r="B21">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>05/21</v>
+        <v>05/31</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -709,49 +709,49 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>05/22</v>
+        <v>06/01</v>
       </c>
       <c r="B23">
-        <v>41.67</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>1480.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>05/23</v>
+        <v>06/02</v>
       </c>
       <c r="B24">
-        <v>41.67</v>
+        <v>8.33</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>1488.2</v>
+        <v>269</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>05/24</v>
+        <v>06/03</v>
       </c>
       <c r="B25">
-        <v>50</v>
+        <v>8.33</v>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>2120.2</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>05/25</v>
+        <v>06/04</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -765,21 +765,21 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>05/26</v>
+        <v>06/05</v>
       </c>
       <c r="B27">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>430.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>05/27</v>
+        <v>06/06</v>
       </c>
       <c r="B28">
         <v>8.33</v>
@@ -788,40 +788,40 @@
         <v>1</v>
       </c>
       <c r="D28">
-        <v>191.2</v>
+        <v>369</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>05/28</v>
+        <v>06/07</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>568</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>05/29</v>
+        <v>06/08</v>
       </c>
       <c r="B30">
-        <v>8.33</v>
+        <v>16.67</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30">
-        <v>329</v>
+        <v>538</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>05/30</v>
+        <v>06/09</v>
       </c>
       <c r="B31">
         <v>8.33</v>
@@ -830,12 +830,12 @@
         <v>1</v>
       </c>
       <c r="D31">
-        <v>329</v>
+        <v>194.65</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>05/31</v>
+        <v>06/10</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -849,111 +849,111 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>06/01</v>
+        <v>06/11</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>83.33</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>06/02</v>
+        <v>06/12</v>
       </c>
       <c r="B34">
-        <v>8.33</v>
+        <v>91.67</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D34">
-        <v>269</v>
+        <v>3139.7999999999997</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>06/03</v>
+        <v>06/13</v>
       </c>
       <c r="B35">
-        <v>8.33</v>
+        <v>91.67</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D35">
-        <v>269</v>
+        <v>3140.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>06/04</v>
+        <v>06/14</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>463.65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>06/05</v>
+        <v>06/15</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>269</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>06/06</v>
+        <v>06/16</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>504.41999999999996</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>06/07</v>
+        <v>06/17</v>
       </c>
       <c r="B39">
-        <v>8.33</v>
+        <v>33.33</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D39">
-        <v>299</v>
+        <v>803.42</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>06/08</v>
+        <v>06/18</v>
       </c>
       <c r="B40">
-        <v>8.33</v>
+        <v>16.67</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40">
         <v>299</v>
@@ -961,21 +961,21 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>06/09</v>
+        <v>06/19</v>
       </c>
       <c r="B41">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>194.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>06/10</v>
+        <v>06/20</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -989,111 +989,111 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>06/11</v>
+        <v>06/21</v>
       </c>
       <c r="B43">
-        <v>83.33</v>
+        <v>8.33</v>
       </c>
       <c r="C43">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D43">
-        <v>2282.9999999999995</v>
+        <v>215.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>06/12</v>
+        <v>06/22</v>
       </c>
       <c r="B44">
-        <v>91.67</v>
+        <v>8.33</v>
       </c>
       <c r="C44">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D44">
-        <v>3139.7999999999997</v>
+        <v>215.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>06/13</v>
+        <v>06/23</v>
       </c>
       <c r="B45">
-        <v>91.67</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>3140.9899999999993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>06/14</v>
+        <v>06/24</v>
       </c>
       <c r="B46">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>269</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>06/15</v>
+        <v>06/25</v>
       </c>
       <c r="B47">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>269</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>06/16</v>
+        <v>06/26</v>
       </c>
       <c r="B48">
-        <v>16.67</v>
+        <v>8.33</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48">
-        <v>504.41999999999996</v>
+        <v>369</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>06/17</v>
+        <v>06/27</v>
       </c>
       <c r="B49">
-        <v>33.33</v>
+        <v>8.33</v>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>803.42</v>
+        <v>369</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>06/18</v>
+        <v>06/28</v>
       </c>
       <c r="B50">
-        <v>16.67</v>
+        <v>8.33</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50">
         <v>299</v>
@@ -1101,7 +1101,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>06/19</v>
+        <v>06/29</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>06/20</v>
+        <v>06/30</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1129,7 +1129,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>06/21</v>
+        <v>07/01</v>
       </c>
       <c r="B53">
         <v>8.33</v>
@@ -1138,12 +1138,12 @@
         <v>1</v>
       </c>
       <c r="D53">
-        <v>215.2</v>
+        <v>299</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>06/22</v>
+        <v>07/02</v>
       </c>
       <c r="B54">
         <v>8.33</v>
@@ -1152,40 +1152,40 @@
         <v>1</v>
       </c>
       <c r="D54">
-        <v>215.2</v>
+        <v>459</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>06/23</v>
+        <v>07/03</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>379</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>06/24</v>
+        <v>07/04</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>379</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>06/25</v>
+        <v>07/05</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1199,7 +1199,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>06/26</v>
+        <v>07/06</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1213,7 +1213,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>06/27</v>
+        <v>07/07</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1227,7 +1227,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>06/28</v>
+        <v>07/08</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>06/29</v>
+        <v>07/09</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1255,35 +1255,35 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>06/30</v>
+        <v>07/10</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>858</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>07/01</v>
+        <v>07/11</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>858</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>07/02</v>
+        <v>07/12</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>07/03</v>
+        <v>07/13</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>07/04</v>
+        <v>07/14</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>07/05</v>
+        <v>07/15</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1339,7 +1339,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>07/06</v>
+        <v>07/16</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1353,35 +1353,35 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>07/07</v>
+        <v>07/17</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>07/08</v>
+        <v>07/18</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>07/09</v>
+        <v>07/19</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1395,35 +1395,35 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>07/10</v>
+        <v>07/20</v>
       </c>
       <c r="B72">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>07/11</v>
+        <v>07/21</v>
       </c>
       <c r="B73">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>07/12</v>
+        <v>07/22</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1437,49 +1437,49 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>07/13</v>
+        <v>07/23</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>329</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>07/14</v>
+        <v>07/24</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>459</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>07/15</v>
+        <v>07/25</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>459</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>07/16</v>
+        <v>07/26</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1493,35 +1493,35 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>07/17</v>
+        <v>07/27</v>
       </c>
       <c r="B79">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="C79">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>1516</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>07/18</v>
+        <v>07/28</v>
       </c>
       <c r="B80">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="C80">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D80">
-        <v>1516</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>07/19</v>
+        <v>07/29</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>07/20</v>
+        <v>07/30</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>07/21</v>
+        <v>07/31</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>07/22</v>
+        <v>08/01</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1577,7 +1577,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>07/23</v>
+        <v>08/02</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>07/24</v>
+        <v>08/03</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>07/25</v>
+        <v>08/04</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>07/26</v>
+        <v>08/05</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>07/27</v>
+        <v>08/06</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1647,7 +1647,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>07/28</v>
+        <v>08/07</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1661,7 +1661,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>07/29</v>
+        <v>08/08</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>07/30</v>
+        <v>08/09</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>07/31</v>
+        <v>08/10</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>08/01</v>
+        <v>08/11</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>08/02</v>
+        <v>08/12</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>08/03</v>
+        <v>08/13</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>08/04</v>
+        <v>08/14</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>08/05</v>
+        <v>08/15</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>08/06</v>
+        <v>08/16</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>08/07</v>
+        <v>08/17</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>08/08</v>
+        <v>08/18</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>08/09</v>
+        <v>08/19</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,7 +1829,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>08/10</v>
+        <v>08/20</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>08/11</v>
+        <v>08/21</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>08/12</v>
+        <v>08/22</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1871,7 +1871,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>08/13</v>
+        <v>08/23</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>08/14</v>
+        <v>08/24</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>08/15</v>
+        <v>08/25</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>08/16</v>
+        <v>08/26</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>08/17</v>
+        <v>08/27</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>08/18</v>
+        <v>08/28</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>08/19</v>
+        <v>08/29</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>08/20</v>
+        <v>08/30</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>08/21</v>
+        <v>08/31</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>08/22</v>
+        <v>09/01</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>08/23</v>
+        <v>09/02</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>08/24</v>
+        <v>09/03</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>08/25</v>
+        <v>09/04</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>08/26</v>
+        <v>09/05</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>08/27</v>
+        <v>09/06</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>08/28</v>
+        <v>09/07</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>08/29</v>
+        <v>09/08</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>08/30</v>
+        <v>09/09</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>08/31</v>
+        <v>09/10</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>09/01</v>
+        <v>09/11</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -2151,7 +2151,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>09/02</v>
+        <v>09/12</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>09/03</v>
+        <v>09/13</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>09/04</v>
+        <v>09/14</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>09/05</v>
+        <v>09/15</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -2207,7 +2207,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>09/06</v>
+        <v>09/16</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>09/07</v>
+        <v>09/17</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>09/08</v>
+        <v>09/18</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>09/09</v>
+        <v>09/19</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -2263,7 +2263,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>09/10</v>
+        <v>09/20</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>09/11</v>
+        <v>09/21</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -2291,7 +2291,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>09/12</v>
+        <v>09/22</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>09/13</v>
+        <v>09/23</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>09/14</v>
+        <v>09/24</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>09/15</v>
+        <v>09/25</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>09/16</v>
+        <v>09/26</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>09/17</v>
+        <v>09/27</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -2375,7 +2375,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>09/18</v>
+        <v>09/28</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -2389,7 +2389,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>09/19</v>
+        <v>09/29</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -2403,7 +2403,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>09/20</v>
+        <v>09/30</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>09/21</v>
+        <v>10/01</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>09/22</v>
+        <v>10/02</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>09/23</v>
+        <v>10/03</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -2459,7 +2459,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>09/24</v>
+        <v>10/04</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -2473,7 +2473,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>09/25</v>
+        <v>10/05</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>09/26</v>
+        <v>10/06</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -2501,7 +2501,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>09/27</v>
+        <v>10/07</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -2515,7 +2515,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>09/28</v>
+        <v>10/08</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>09/29</v>
+        <v>10/09</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>09/30</v>
+        <v>10/10</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -2552,12 +2552,306 @@
         <v>0</v>
       </c>
       <c r="D154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>10/11</v>
+      </c>
+      <c r="B155">
+        <v>0</v>
+      </c>
+      <c r="C155">
+        <v>0</v>
+      </c>
+      <c r="D155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>10/12</v>
+      </c>
+      <c r="B156">
+        <v>0</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
+      <c r="D156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>10/13</v>
+      </c>
+      <c r="B157">
+        <v>0</v>
+      </c>
+      <c r="C157">
+        <v>0</v>
+      </c>
+      <c r="D157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>10/14</v>
+      </c>
+      <c r="B158">
+        <v>0</v>
+      </c>
+      <c r="C158">
+        <v>0</v>
+      </c>
+      <c r="D158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>10/15</v>
+      </c>
+      <c r="B159">
+        <v>0</v>
+      </c>
+      <c r="C159">
+        <v>0</v>
+      </c>
+      <c r="D159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>10/16</v>
+      </c>
+      <c r="B160">
+        <v>0</v>
+      </c>
+      <c r="C160">
+        <v>0</v>
+      </c>
+      <c r="D160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>10/17</v>
+      </c>
+      <c r="B161">
+        <v>0</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+      <c r="D161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>10/18</v>
+      </c>
+      <c r="B162">
+        <v>0</v>
+      </c>
+      <c r="C162">
+        <v>0</v>
+      </c>
+      <c r="D162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>10/19</v>
+      </c>
+      <c r="B163">
+        <v>0</v>
+      </c>
+      <c r="C163">
+        <v>0</v>
+      </c>
+      <c r="D163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>10/20</v>
+      </c>
+      <c r="B164">
+        <v>0</v>
+      </c>
+      <c r="C164">
+        <v>0</v>
+      </c>
+      <c r="D164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>10/21</v>
+      </c>
+      <c r="B165">
+        <v>0</v>
+      </c>
+      <c r="C165">
+        <v>0</v>
+      </c>
+      <c r="D165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>10/22</v>
+      </c>
+      <c r="B166">
+        <v>0</v>
+      </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
+      <c r="D166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>10/23</v>
+      </c>
+      <c r="B167">
+        <v>0</v>
+      </c>
+      <c r="C167">
+        <v>0</v>
+      </c>
+      <c r="D167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>10/24</v>
+      </c>
+      <c r="B168">
+        <v>0</v>
+      </c>
+      <c r="C168">
+        <v>0</v>
+      </c>
+      <c r="D168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>10/25</v>
+      </c>
+      <c r="B169">
+        <v>0</v>
+      </c>
+      <c r="C169">
+        <v>0</v>
+      </c>
+      <c r="D169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>10/26</v>
+      </c>
+      <c r="B170">
+        <v>0</v>
+      </c>
+      <c r="C170">
+        <v>0</v>
+      </c>
+      <c r="D170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>10/27</v>
+      </c>
+      <c r="B171">
+        <v>0</v>
+      </c>
+      <c r="C171">
+        <v>0</v>
+      </c>
+      <c r="D171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>10/28</v>
+      </c>
+      <c r="B172">
+        <v>0</v>
+      </c>
+      <c r="C172">
+        <v>0</v>
+      </c>
+      <c r="D172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>10/29</v>
+      </c>
+      <c r="B173">
+        <v>0</v>
+      </c>
+      <c r="C173">
+        <v>0</v>
+      </c>
+      <c r="D173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>10/30</v>
+      </c>
+      <c r="B174">
+        <v>0</v>
+      </c>
+      <c r="C174">
+        <v>0</v>
+      </c>
+      <c r="D174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>10/31</v>
+      </c>
+      <c r="B175">
+        <v>0</v>
+      </c>
+      <c r="C175">
+        <v>0</v>
+      </c>
+      <c r="D175">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D154"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D175"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ok-fc_occupancy_pace_150day.xlsx
+++ b/ok-fc_occupancy_pace_150day.xlsx
@@ -397,277 +397,277 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D175"/>
+  <dimension ref="A1:D155"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Date</v>
       </c>
       <c r="B1" t="str">
-        <v>Rooms Occupied Year 2026</v>
+        <v>ADR 2026</v>
       </c>
       <c r="C1" t="str">
         <v>ACCOMMODATIONS BOOKED 2026</v>
       </c>
       <c r="D1" t="str">
-        <v>Revenue 2026</v>
+        <v>Room Rates 2026</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>05/11</v>
+        <v>06/01</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>177.825</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>355.65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>05/12</v>
+        <v>06/02</v>
       </c>
       <c r="B3">
-        <v>8.33</v>
+        <v>269</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
-        <v>203.15</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>05/13</v>
+        <v>06/03</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>05/14</v>
+        <v>06/04</v>
       </c>
       <c r="B5">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>05/15</v>
+        <v>06/05</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>05/16</v>
+        <v>06/06</v>
       </c>
       <c r="B7">
-        <v>16.67</v>
+        <v>275.58666666666664</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>568.8</v>
+        <v>826.76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>05/17</v>
+        <v>06/07</v>
       </c>
       <c r="B8">
-        <v>16.67</v>
+        <v>250.33333333333334</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8">
-        <v>454.1</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>05/18</v>
+        <v>06/08</v>
       </c>
       <c r="B9">
-        <v>8.33</v>
+        <v>299</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9">
-        <v>215.1</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>05/19</v>
+        <v>06/09</v>
       </c>
       <c r="B10">
-        <v>16.67</v>
+        <v>144.54999999999998</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>454.1</v>
+        <v>433.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>05/20</v>
+        <v>06/10</v>
       </c>
       <c r="B11">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11">
-        <v>239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>05/21</v>
+        <v>06/11</v>
       </c>
       <c r="B12">
-        <v>16.67</v>
+        <v>241.1</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12">
-        <v>394.2</v>
+        <v>723.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>05/22</v>
+        <v>06/12</v>
       </c>
       <c r="B13">
-        <v>58.33</v>
+        <v>255.525</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D13">
-        <v>2107.45</v>
+        <v>1022.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>05/23</v>
+        <v>06/13</v>
       </c>
       <c r="B14">
-        <v>66.67</v>
+        <v>255.8225</v>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>2456.5499999999997</v>
+        <v>1023.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>05/24</v>
+        <v>06/14</v>
       </c>
       <c r="B15">
-        <v>66.67</v>
+        <v>214.86249999999998</v>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D15">
-        <v>2783.45</v>
+        <v>859.4499999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>05/25</v>
+        <v>06/15</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>219.5</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>439</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>05/26</v>
+        <v>06/16</v>
       </c>
       <c r="B17">
-        <v>50</v>
+        <v>252.20999999999998</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>1395.4</v>
+        <v>504.41999999999996</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>05/27</v>
+        <v>06/17</v>
       </c>
       <c r="B18">
-        <v>25</v>
+        <v>260.605</v>
       </c>
       <c r="C18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18">
-        <v>659.2</v>
+        <v>1042.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>05/28</v>
+        <v>06/18</v>
       </c>
       <c r="B19">
-        <v>8.33</v>
+        <v>269</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>199</v>
+        <v>538</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>05/29</v>
+        <v>06/19</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -681,7 +681,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>05/30</v>
+        <v>06/20</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -695,63 +695,63 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>05/31</v>
+        <v>06/21</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>246.925</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>987.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>06/01</v>
+        <v>06/22</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>214.29999999999998</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>642.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>06/02</v>
+        <v>06/23</v>
       </c>
       <c r="B24">
-        <v>8.33</v>
+        <v>229.075</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D24">
-        <v>269</v>
+        <v>916.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>06/03</v>
+        <v>06/24</v>
       </c>
       <c r="B25">
-        <v>8.33</v>
+        <v>226.375</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D25">
-        <v>269</v>
+        <v>905.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>06/04</v>
+        <v>06/25</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -765,259 +765,259 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>06/05</v>
+        <v>06/26</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>318.2</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>954.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>06/06</v>
+        <v>06/27</v>
       </c>
       <c r="B28">
-        <v>8.33</v>
+        <v>315.75</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D28">
-        <v>369</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>06/07</v>
+        <v>06/28</v>
       </c>
       <c r="B29">
-        <v>16.67</v>
+        <v>299</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>568</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>06/08</v>
+        <v>06/29</v>
       </c>
       <c r="B30">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>06/09</v>
+        <v>06/30</v>
       </c>
       <c r="B31">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>194.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>06/10</v>
+        <v>07/01</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>06/11</v>
+        <v>07/02</v>
       </c>
       <c r="B33">
-        <v>83.33</v>
+        <v>459</v>
       </c>
       <c r="C33">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>2283</v>
+        <v>459</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>06/12</v>
+        <v>07/03</v>
       </c>
       <c r="B34">
-        <v>91.67</v>
+        <v>379</v>
       </c>
       <c r="C34">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>3139.7999999999997</v>
+        <v>379</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>06/13</v>
+        <v>07/04</v>
       </c>
       <c r="B35">
-        <v>91.67</v>
+        <v>379</v>
       </c>
       <c r="C35">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>3140.99</v>
+        <v>379</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>06/14</v>
+        <v>07/05</v>
       </c>
       <c r="B36">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>463.65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>06/15</v>
+        <v>07/06</v>
       </c>
       <c r="B37">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>269</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>06/16</v>
+        <v>07/07</v>
       </c>
       <c r="B38">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>504.41999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>06/17</v>
+        <v>07/08</v>
       </c>
       <c r="B39">
-        <v>33.33</v>
+        <v>257.55</v>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>803.42</v>
+        <v>257.55</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>06/18</v>
+        <v>07/09</v>
       </c>
       <c r="B40">
-        <v>16.67</v>
+        <v>311.125</v>
       </c>
       <c r="C40">
         <v>2</v>
       </c>
       <c r="D40">
-        <v>299</v>
+        <v>622.25</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>06/19</v>
+        <v>07/10</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>06/20</v>
+        <v>07/11</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>439</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>06/21</v>
+        <v>07/12</v>
       </c>
       <c r="B43">
-        <v>8.33</v>
+        <v>250</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="D43">
-        <v>215.2</v>
+        <v>250</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>06/22</v>
+        <v>07/13</v>
       </c>
       <c r="B44">
-        <v>8.33</v>
+        <v>229</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
       <c r="D44">
-        <v>215.2</v>
+        <v>229</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>06/23</v>
+        <v>07/14</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>06/24</v>
+        <v>07/15</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>06/25</v>
+        <v>07/16</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1059,49 +1059,49 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>06/26</v>
+        <v>07/17</v>
       </c>
       <c r="B48">
-        <v>8.33</v>
+        <v>379</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D48">
-        <v>369</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>06/27</v>
+        <v>07/18</v>
       </c>
       <c r="B49">
-        <v>8.33</v>
+        <v>379</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D49">
-        <v>369</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>06/28</v>
+        <v>07/19</v>
       </c>
       <c r="B50">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>06/29</v>
+        <v>07/20</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>06/30</v>
+        <v>07/21</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1129,105 +1129,105 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>07/01</v>
+        <v>07/22</v>
       </c>
       <c r="B53">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>07/02</v>
+        <v>07/23</v>
       </c>
       <c r="B54">
-        <v>8.33</v>
+        <v>329</v>
       </c>
       <c r="C54">
         <v>1</v>
       </c>
       <c r="D54">
-        <v>459</v>
+        <v>329</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>07/03</v>
+        <v>07/24</v>
       </c>
       <c r="B55">
-        <v>8.33</v>
+        <v>406.5</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55">
-        <v>379</v>
+        <v>813</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>07/04</v>
+        <v>07/25</v>
       </c>
       <c r="B56">
-        <v>8.33</v>
+        <v>389</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56">
-        <v>379</v>
+        <v>778</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>07/05</v>
+        <v>07/26</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>187</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>07/06</v>
+        <v>07/27</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>07/07</v>
+        <v>07/28</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>168</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>07/08</v>
+        <v>07/29</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>07/09</v>
+        <v>07/30</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1255,35 +1255,35 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>07/10</v>
+        <v>07/31</v>
       </c>
       <c r="B62">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>858</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>07/11</v>
+        <v>08/01</v>
       </c>
       <c r="B63">
-        <v>16.67</v>
+        <v>0</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>858</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>07/12</v>
+        <v>08/02</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>07/13</v>
+        <v>08/03</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>07/14</v>
+        <v>08/04</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>07/15</v>
+        <v>08/05</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1339,7 +1339,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>07/16</v>
+        <v>08/06</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1353,35 +1353,35 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>07/17</v>
+        <v>08/07</v>
       </c>
       <c r="B69">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="C69">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>1516</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>07/18</v>
+        <v>08/08</v>
       </c>
       <c r="B70">
-        <v>33.33</v>
+        <v>0</v>
       </c>
       <c r="C70">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>1516</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>07/19</v>
+        <v>08/09</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>07/20</v>
+        <v>08/10</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>07/21</v>
+        <v>08/11</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>07/22</v>
+        <v>08/12</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1437,49 +1437,49 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>07/23</v>
+        <v>08/13</v>
       </c>
       <c r="B75">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>07/24</v>
+        <v>08/14</v>
       </c>
       <c r="B76">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>07/25</v>
+        <v>08/15</v>
       </c>
       <c r="B77">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>07/26</v>
+        <v>08/16</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1493,7 +1493,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>07/27</v>
+        <v>08/17</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1507,7 +1507,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>07/28</v>
+        <v>08/18</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>07/29</v>
+        <v>08/19</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>07/30</v>
+        <v>08/20</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>07/31</v>
+        <v>08/21</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>08/01</v>
+        <v>08/22</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1577,7 +1577,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>08/02</v>
+        <v>08/23</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>08/03</v>
+        <v>08/24</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>08/04</v>
+        <v>08/25</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>08/05</v>
+        <v>08/26</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>08/06</v>
+        <v>08/27</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1647,7 +1647,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>08/07</v>
+        <v>08/28</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1661,7 +1661,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>08/08</v>
+        <v>08/29</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>08/09</v>
+        <v>08/30</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>08/10</v>
+        <v>08/31</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>08/11</v>
+        <v>09/01</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>08/12</v>
+        <v>09/02</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>08/13</v>
+        <v>09/03</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>08/14</v>
+        <v>09/04</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>08/15</v>
+        <v>09/05</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>08/16</v>
+        <v>09/06</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>08/17</v>
+        <v>09/07</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>08/18</v>
+        <v>09/08</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>08/19</v>
+        <v>09/09</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,7 +1829,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>08/20</v>
+        <v>09/10</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>08/21</v>
+        <v>09/11</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>08/22</v>
+        <v>09/12</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1871,7 +1871,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>08/23</v>
+        <v>09/13</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>08/24</v>
+        <v>09/14</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>08/25</v>
+        <v>09/15</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>08/26</v>
+        <v>09/16</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>08/27</v>
+        <v>09/17</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>08/28</v>
+        <v>09/18</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>08/29</v>
+        <v>09/19</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>08/30</v>
+        <v>09/20</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>08/31</v>
+        <v>09/21</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>09/01</v>
+        <v>09/22</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>09/02</v>
+        <v>09/23</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>09/03</v>
+        <v>09/24</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>09/04</v>
+        <v>09/25</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>09/05</v>
+        <v>09/26</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>09/06</v>
+        <v>09/27</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>09/07</v>
+        <v>09/28</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>09/08</v>
+        <v>09/29</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>09/09</v>
+        <v>09/30</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>09/10</v>
+        <v>10/01</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>09/11</v>
+        <v>10/02</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -2151,7 +2151,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>09/12</v>
+        <v>10/03</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>09/13</v>
+        <v>10/04</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>09/14</v>
+        <v>10/05</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>09/15</v>
+        <v>10/06</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -2207,7 +2207,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>09/16</v>
+        <v>10/07</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>09/17</v>
+        <v>10/08</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>09/18</v>
+        <v>10/09</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>09/19</v>
+        <v>10/10</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -2263,7 +2263,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>09/20</v>
+        <v>10/11</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>09/21</v>
+        <v>10/12</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -2291,7 +2291,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>09/22</v>
+        <v>10/13</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>09/23</v>
+        <v>10/14</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>09/24</v>
+        <v>10/15</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>09/25</v>
+        <v>10/16</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>09/26</v>
+        <v>10/17</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>09/27</v>
+        <v>10/18</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -2375,7 +2375,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>09/28</v>
+        <v>10/19</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -2389,7 +2389,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>09/29</v>
+        <v>10/20</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -2403,7 +2403,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>09/30</v>
+        <v>10/21</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>10/01</v>
+        <v>10/22</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>10/02</v>
+        <v>10/23</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>10/03</v>
+        <v>10/24</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -2459,7 +2459,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>10/04</v>
+        <v>10/25</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -2473,7 +2473,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>10/05</v>
+        <v>10/26</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>10/06</v>
+        <v>10/27</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -2501,7 +2501,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>10/07</v>
+        <v>10/28</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -2515,7 +2515,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>10/08</v>
+        <v>10/29</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>10/09</v>
+        <v>10/30</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>10/10</v>
+        <v>10/31</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -2557,7 +2557,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>10/11</v>
+        <v>11/01</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -2566,292 +2566,12 @@
         <v>0</v>
       </c>
       <c r="D155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="str">
-        <v>10/12</v>
-      </c>
-      <c r="B156">
-        <v>0</v>
-      </c>
-      <c r="C156">
-        <v>0</v>
-      </c>
-      <c r="D156">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="str">
-        <v>10/13</v>
-      </c>
-      <c r="B157">
-        <v>0</v>
-      </c>
-      <c r="C157">
-        <v>0</v>
-      </c>
-      <c r="D157">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="str">
-        <v>10/14</v>
-      </c>
-      <c r="B158">
-        <v>0</v>
-      </c>
-      <c r="C158">
-        <v>0</v>
-      </c>
-      <c r="D158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="str">
-        <v>10/15</v>
-      </c>
-      <c r="B159">
-        <v>0</v>
-      </c>
-      <c r="C159">
-        <v>0</v>
-      </c>
-      <c r="D159">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="str">
-        <v>10/16</v>
-      </c>
-      <c r="B160">
-        <v>0</v>
-      </c>
-      <c r="C160">
-        <v>0</v>
-      </c>
-      <c r="D160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="str">
-        <v>10/17</v>
-      </c>
-      <c r="B161">
-        <v>0</v>
-      </c>
-      <c r="C161">
-        <v>0</v>
-      </c>
-      <c r="D161">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="str">
-        <v>10/18</v>
-      </c>
-      <c r="B162">
-        <v>0</v>
-      </c>
-      <c r="C162">
-        <v>0</v>
-      </c>
-      <c r="D162">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="str">
-        <v>10/19</v>
-      </c>
-      <c r="B163">
-        <v>0</v>
-      </c>
-      <c r="C163">
-        <v>0</v>
-      </c>
-      <c r="D163">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="str">
-        <v>10/20</v>
-      </c>
-      <c r="B164">
-        <v>0</v>
-      </c>
-      <c r="C164">
-        <v>0</v>
-      </c>
-      <c r="D164">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="str">
-        <v>10/21</v>
-      </c>
-      <c r="B165">
-        <v>0</v>
-      </c>
-      <c r="C165">
-        <v>0</v>
-      </c>
-      <c r="D165">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="str">
-        <v>10/22</v>
-      </c>
-      <c r="B166">
-        <v>0</v>
-      </c>
-      <c r="C166">
-        <v>0</v>
-      </c>
-      <c r="D166">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="str">
-        <v>10/23</v>
-      </c>
-      <c r="B167">
-        <v>0</v>
-      </c>
-      <c r="C167">
-        <v>0</v>
-      </c>
-      <c r="D167">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="str">
-        <v>10/24</v>
-      </c>
-      <c r="B168">
-        <v>0</v>
-      </c>
-      <c r="C168">
-        <v>0</v>
-      </c>
-      <c r="D168">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="str">
-        <v>10/25</v>
-      </c>
-      <c r="B169">
-        <v>0</v>
-      </c>
-      <c r="C169">
-        <v>0</v>
-      </c>
-      <c r="D169">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="str">
-        <v>10/26</v>
-      </c>
-      <c r="B170">
-        <v>0</v>
-      </c>
-      <c r="C170">
-        <v>0</v>
-      </c>
-      <c r="D170">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="str">
-        <v>10/27</v>
-      </c>
-      <c r="B171">
-        <v>0</v>
-      </c>
-      <c r="C171">
-        <v>0</v>
-      </c>
-      <c r="D171">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="str">
-        <v>10/28</v>
-      </c>
-      <c r="B172">
-        <v>0</v>
-      </c>
-      <c r="C172">
-        <v>0</v>
-      </c>
-      <c r="D172">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="str">
-        <v>10/29</v>
-      </c>
-      <c r="B173">
-        <v>0</v>
-      </c>
-      <c r="C173">
-        <v>0</v>
-      </c>
-      <c r="D173">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="str">
-        <v>10/30</v>
-      </c>
-      <c r="B174">
-        <v>0</v>
-      </c>
-      <c r="C174">
-        <v>0</v>
-      </c>
-      <c r="D174">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="str">
-        <v>10/31</v>
-      </c>
-      <c r="B175">
-        <v>0</v>
-      </c>
-      <c r="C175">
-        <v>0</v>
-      </c>
-      <c r="D175">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D175"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D155"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ok-fc_occupancy_pace_150day.xlsx
+++ b/ok-fc_occupancy_pace_150day.xlsx
@@ -415,413 +415,413 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>06/01</v>
+        <v>06/15</v>
       </c>
       <c r="B2">
-        <v>177.825</v>
+        <v>205.05</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>355.65</v>
+        <v>820.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>06/02</v>
+        <v>06/16</v>
       </c>
       <c r="B3">
-        <v>269</v>
+        <v>205.704</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>269</v>
+        <v>1028.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>06/03</v>
+        <v>06/17</v>
       </c>
       <c r="B4">
-        <v>269</v>
+        <v>217.30125</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>269</v>
+        <v>1738.41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>06/04</v>
+        <v>06/18</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>265.5</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>06/05</v>
+        <v>06/19</v>
       </c>
       <c r="B6">
-        <v>290</v>
+        <v>349.65</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>290</v>
+        <v>1398.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>06/06</v>
+        <v>06/20</v>
       </c>
       <c r="B7">
-        <v>275.58666666666664</v>
+        <v>330.925</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7">
-        <v>826.76</v>
+        <v>1323.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>06/07</v>
+        <v>06/21</v>
       </c>
       <c r="B8">
-        <v>250.33333333333334</v>
+        <v>249.15</v>
       </c>
       <c r="C8">
         <v>6</v>
       </c>
       <c r="D8">
-        <v>1502</v>
+        <v>1494.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>06/08</v>
+        <v>06/22</v>
       </c>
       <c r="B9">
-        <v>299</v>
+        <v>232.975</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>299</v>
+        <v>931.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>06/09</v>
+        <v>06/23</v>
       </c>
       <c r="B10">
-        <v>144.54999999999998</v>
+        <v>215.66</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10">
-        <v>433.65</v>
+        <v>1078.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>06/10</v>
+        <v>06/24</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>223.1</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1115.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>06/11</v>
+        <v>06/25</v>
       </c>
       <c r="B12">
-        <v>241.1</v>
+        <v>322</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>723.3</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>06/12</v>
+        <v>06/26</v>
       </c>
       <c r="B13">
-        <v>255.525</v>
+        <v>330.75</v>
       </c>
       <c r="C13">
         <v>4</v>
       </c>
       <c r="D13">
-        <v>1022.1</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>06/13</v>
+        <v>06/27</v>
       </c>
       <c r="B14">
-        <v>255.8225</v>
+        <v>306.26000000000005</v>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14">
-        <v>1023.29</v>
+        <v>1531.3000000000002</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>06/14</v>
+        <v>06/28</v>
       </c>
       <c r="B15">
-        <v>214.86249999999998</v>
+        <v>297.5</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>859.4499999999999</v>
+        <v>595</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>06/15</v>
+        <v>06/29</v>
       </c>
       <c r="B16">
-        <v>219.5</v>
+        <v>288</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
       <c r="D16">
-        <v>439</v>
+        <v>576</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>06/16</v>
+        <v>06/30</v>
       </c>
       <c r="B17">
-        <v>252.20999999999998</v>
+        <v>279.5</v>
       </c>
       <c r="C17">
         <v>2</v>
       </c>
       <c r="D17">
-        <v>504.41999999999996</v>
+        <v>559</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>06/17</v>
+        <v>07/01</v>
       </c>
       <c r="B18">
-        <v>260.605</v>
+        <v>299</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>1042.42</v>
+        <v>299</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>06/18</v>
+        <v>07/02</v>
       </c>
       <c r="B19">
-        <v>269</v>
+        <v>361.5</v>
       </c>
       <c r="C19">
         <v>2</v>
       </c>
       <c r="D19">
-        <v>538</v>
+        <v>723</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>06/19</v>
+        <v>07/03</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>372</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>744</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>06/20</v>
+        <v>07/04</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>738</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>06/21</v>
+        <v>07/05</v>
       </c>
       <c r="B22">
-        <v>246.925</v>
+        <v>276</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>987.7</v>
+        <v>276</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>06/22</v>
+        <v>07/06</v>
       </c>
       <c r="B23">
-        <v>214.29999999999998</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>642.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>06/23</v>
+        <v>07/07</v>
       </c>
       <c r="B24">
-        <v>229.075</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>916.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>06/24</v>
+        <v>07/08</v>
       </c>
       <c r="B25">
-        <v>226.375</v>
+        <v>243.275</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>905.5</v>
+        <v>486.55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>06/25</v>
+        <v>07/09</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>295.75</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>887.25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>06/26</v>
+        <v>07/10</v>
       </c>
       <c r="B27">
-        <v>318.2</v>
+        <v>314.14</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D27">
-        <v>954.6</v>
+        <v>3141.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>06/27</v>
+        <v>07/11</v>
       </c>
       <c r="B28">
-        <v>315.75</v>
+        <v>310.46999999999997</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D28">
-        <v>1263</v>
+        <v>3104.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>06/28</v>
+        <v>07/12</v>
       </c>
       <c r="B29">
-        <v>299</v>
+        <v>259.6666666666667</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29">
-        <v>299</v>
+        <v>779</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>06/29</v>
+        <v>07/13</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>488</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>06/30</v>
+        <v>07/14</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -835,63 +835,63 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>07/01</v>
+        <v>07/15</v>
       </c>
       <c r="B32">
-        <v>299</v>
+        <v>250</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32">
-        <v>299</v>
+        <v>250</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>07/02</v>
+        <v>07/16</v>
       </c>
       <c r="B33">
-        <v>459</v>
+        <v>259.5</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33">
-        <v>459</v>
+        <v>519</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>07/03</v>
+        <v>07/17</v>
       </c>
       <c r="B34">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D34">
-        <v>379</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>07/04</v>
+        <v>07/18</v>
       </c>
       <c r="B35">
-        <v>379</v>
+        <v>384.8333333333333</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D35">
-        <v>379</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>07/05</v>
+        <v>07/19</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>07/06</v>
+        <v>07/20</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -919,7 +919,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>07/07</v>
+        <v>07/21</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -933,105 +933,105 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>07/08</v>
+        <v>07/22</v>
       </c>
       <c r="B39">
-        <v>257.55</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>257.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>07/09</v>
+        <v>07/23</v>
       </c>
       <c r="B40">
-        <v>311.125</v>
+        <v>329</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D40">
-        <v>622.25</v>
+        <v>329</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>07/10</v>
+        <v>07/24</v>
       </c>
       <c r="B41">
-        <v>439</v>
+        <v>406.5</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41">
-        <v>1317</v>
+        <v>813</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>07/11</v>
+        <v>07/25</v>
       </c>
       <c r="B42">
-        <v>439</v>
+        <v>389</v>
       </c>
       <c r="C42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D42">
-        <v>1317</v>
+        <v>778</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>07/12</v>
+        <v>07/26</v>
       </c>
       <c r="B43">
-        <v>250</v>
+        <v>254.25</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D43">
-        <v>250</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>07/13</v>
+        <v>07/27</v>
       </c>
       <c r="B44">
-        <v>229</v>
+        <v>162</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
       <c r="D44">
-        <v>229</v>
+        <v>162</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>07/14</v>
+        <v>07/28</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>168</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>07/15</v>
+        <v>07/29</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>07/16</v>
+        <v>07/30</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1059,35 +1059,35 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>07/17</v>
+        <v>07/31</v>
       </c>
       <c r="B48">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>1516</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>07/18</v>
+        <v>08/01</v>
       </c>
       <c r="B49">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>1516</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>07/19</v>
+        <v>08/02</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1101,7 +1101,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>07/20</v>
+        <v>08/03</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>07/21</v>
+        <v>08/04</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1129,7 +1129,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>07/22</v>
+        <v>08/05</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1143,91 +1143,91 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>07/23</v>
+        <v>08/06</v>
       </c>
       <c r="B54">
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>07/24</v>
+        <v>08/07</v>
       </c>
       <c r="B55">
-        <v>406.5</v>
+        <v>0</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>07/25</v>
+        <v>08/08</v>
       </c>
       <c r="B56">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>07/26</v>
+        <v>08/09</v>
       </c>
       <c r="B57">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>07/27</v>
+        <v>08/10</v>
       </c>
       <c r="B58">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>07/28</v>
+        <v>08/11</v>
       </c>
       <c r="B59">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>07/29</v>
+        <v>08/12</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>07/30</v>
+        <v>08/13</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>07/31</v>
+        <v>08/14</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1269,35 +1269,35 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>08/01</v>
+        <v>08/15</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>223.2</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>223.2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>08/02</v>
+        <v>08/16</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>167.4</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>167.4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>08/03</v>
+        <v>08/17</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>08/04</v>
+        <v>08/18</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>08/05</v>
+        <v>08/19</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1339,7 +1339,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>08/06</v>
+        <v>08/20</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>08/07</v>
+        <v>08/21</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1367,7 +1367,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>08/08</v>
+        <v>08/22</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>08/09</v>
+        <v>08/23</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>08/10</v>
+        <v>08/24</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>08/11</v>
+        <v>08/25</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>08/12</v>
+        <v>08/26</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>08/13</v>
+        <v>08/27</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>08/14</v>
+        <v>08/28</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>08/15</v>
+        <v>08/29</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>08/16</v>
+        <v>08/30</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1493,7 +1493,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>08/17</v>
+        <v>08/31</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1507,7 +1507,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>08/18</v>
+        <v>09/01</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>08/19</v>
+        <v>09/02</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>08/20</v>
+        <v>09/03</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>08/21</v>
+        <v>09/04</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>08/22</v>
+        <v>09/05</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1577,7 +1577,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>08/23</v>
+        <v>09/06</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>08/24</v>
+        <v>09/07</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>08/25</v>
+        <v>09/08</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>08/26</v>
+        <v>09/09</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>08/27</v>
+        <v>09/10</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1647,7 +1647,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>08/28</v>
+        <v>09/11</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1661,7 +1661,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>08/29</v>
+        <v>09/12</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>08/30</v>
+        <v>09/13</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>08/31</v>
+        <v>09/14</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>09/01</v>
+        <v>09/15</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>09/02</v>
+        <v>09/16</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>09/03</v>
+        <v>09/17</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>09/04</v>
+        <v>09/18</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>09/05</v>
+        <v>09/19</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>09/06</v>
+        <v>09/20</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>09/07</v>
+        <v>09/21</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>09/08</v>
+        <v>09/22</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>09/09</v>
+        <v>09/23</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,7 +1829,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>09/10</v>
+        <v>09/24</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1843,35 +1843,35 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>09/11</v>
+        <v>09/25</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>262.5</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>09/12</v>
+        <v>09/26</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>262.5</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>09/13</v>
+        <v>09/27</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>09/14</v>
+        <v>09/28</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>09/15</v>
+        <v>09/29</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>09/16</v>
+        <v>09/30</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>09/17</v>
+        <v>10/01</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>09/18</v>
+        <v>10/02</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>09/19</v>
+        <v>10/03</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>09/20</v>
+        <v>10/04</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>09/21</v>
+        <v>10/05</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>09/22</v>
+        <v>10/06</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>09/23</v>
+        <v>10/07</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>09/24</v>
+        <v>10/08</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>09/25</v>
+        <v>10/09</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>09/26</v>
+        <v>10/10</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>09/27</v>
+        <v>10/11</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>09/28</v>
+        <v>10/12</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>09/29</v>
+        <v>10/13</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>09/30</v>
+        <v>10/14</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>10/01</v>
+        <v>10/15</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>10/02</v>
+        <v>10/16</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -2151,7 +2151,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>10/03</v>
+        <v>10/17</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>10/04</v>
+        <v>10/18</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>10/05</v>
+        <v>10/19</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>10/06</v>
+        <v>10/20</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -2207,7 +2207,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>10/07</v>
+        <v>10/21</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>10/08</v>
+        <v>10/22</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>10/09</v>
+        <v>10/23</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>10/10</v>
+        <v>10/24</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -2263,7 +2263,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>10/11</v>
+        <v>10/25</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>10/12</v>
+        <v>10/26</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -2291,7 +2291,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>10/13</v>
+        <v>10/27</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>10/14</v>
+        <v>10/28</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>10/15</v>
+        <v>10/29</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>10/16</v>
+        <v>10/30</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>10/17</v>
+        <v>10/31</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>10/18</v>
+        <v>11/01</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -2375,7 +2375,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>10/19</v>
+        <v>11/02</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -2389,7 +2389,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>10/20</v>
+        <v>11/03</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -2403,7 +2403,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>10/21</v>
+        <v>11/04</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>10/22</v>
+        <v>11/05</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>10/23</v>
+        <v>11/06</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>10/24</v>
+        <v>11/07</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -2459,7 +2459,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>10/25</v>
+        <v>11/08</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -2473,7 +2473,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>10/26</v>
+        <v>11/09</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>10/27</v>
+        <v>11/10</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -2501,7 +2501,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>10/28</v>
+        <v>11/11</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -2515,7 +2515,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>10/29</v>
+        <v>11/12</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -2529,35 +2529,35 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>10/30</v>
+        <v>11/13</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>384.5</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D153">
-        <v>0</v>
+        <v>769</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>10/31</v>
+        <v>11/14</v>
       </c>
       <c r="B154">
-        <v>0</v>
+        <v>400.5</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D154">
-        <v>0</v>
+        <v>801</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>11/01</v>
+        <v>11/15</v>
       </c>
       <c r="B155">
         <v>0</v>

--- a/ok-fc_occupancy_pace_150day.xlsx
+++ b/ok-fc_occupancy_pace_150day.xlsx
@@ -415,315 +415,315 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>06/15</v>
+        <v>06/22</v>
       </c>
       <c r="B2">
-        <v>205.05</v>
+        <v>220.18</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2">
-        <v>820.2</v>
+        <v>1100.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>06/16</v>
+        <v>06/23</v>
       </c>
       <c r="B3">
-        <v>205.704</v>
+        <v>207.88333333333333</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>1028.52</v>
+        <v>1247.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>06/17</v>
+        <v>06/24</v>
       </c>
       <c r="B4">
-        <v>217.30125</v>
+        <v>223.1</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D4">
-        <v>1738.41</v>
+        <v>1115.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>06/18</v>
+        <v>06/25</v>
       </c>
       <c r="B5">
-        <v>265.5</v>
+        <v>322</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>1062</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>06/19</v>
+        <v>06/26</v>
       </c>
       <c r="B6">
-        <v>349.65</v>
+        <v>293.86666666666673</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>1398.6</v>
+        <v>1763.2000000000003</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>06/20</v>
+        <v>06/27</v>
       </c>
       <c r="B7">
-        <v>330.925</v>
+        <v>283.14285714285717</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>1323.7</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>06/21</v>
+        <v>06/28</v>
       </c>
       <c r="B8">
-        <v>249.15</v>
+        <v>297.5</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>1494.9</v>
+        <v>595</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>06/22</v>
+        <v>06/29</v>
       </c>
       <c r="B9">
-        <v>232.975</v>
+        <v>288</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>931.9</v>
+        <v>576</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>06/23</v>
+        <v>06/30</v>
       </c>
       <c r="B10">
-        <v>215.66</v>
+        <v>279.5</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>1078.3</v>
+        <v>559</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>06/24</v>
+        <v>07/01</v>
       </c>
       <c r="B11">
-        <v>223.1</v>
+        <v>299</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>1115.5</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>06/25</v>
+        <v>07/02</v>
       </c>
       <c r="B12">
-        <v>322</v>
+        <v>371.3333333333333</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12">
-        <v>322</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>06/26</v>
+        <v>07/03</v>
       </c>
       <c r="B13">
-        <v>330.75</v>
+        <v>399</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13">
-        <v>1323</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>06/27</v>
+        <v>07/04</v>
       </c>
       <c r="B14">
-        <v>306.26000000000005</v>
+        <v>398.3333333333333</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14">
-        <v>1531.3000000000002</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>06/28</v>
+        <v>07/05</v>
       </c>
       <c r="B15">
-        <v>297.5</v>
+        <v>246</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
       <c r="D15">
-        <v>595</v>
+        <v>492</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>06/29</v>
+        <v>07/06</v>
       </c>
       <c r="B16">
-        <v>288</v>
+        <v>197</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>576</v>
+        <v>197</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>06/30</v>
+        <v>07/07</v>
       </c>
       <c r="B17">
-        <v>279.5</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>07/01</v>
+        <v>07/08</v>
       </c>
       <c r="B18">
-        <v>299</v>
+        <v>243.275</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>299</v>
+        <v>486.55</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>07/02</v>
+        <v>07/09</v>
       </c>
       <c r="B19">
-        <v>361.5</v>
+        <v>295.75</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19">
-        <v>723</v>
+        <v>887.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>07/03</v>
+        <v>07/10</v>
       </c>
       <c r="B20">
-        <v>372</v>
+        <v>314.14</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D20">
-        <v>744</v>
+        <v>3141.3999999999996</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>07/04</v>
+        <v>07/11</v>
       </c>
       <c r="B21">
-        <v>369</v>
+        <v>310.46999999999997</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D21">
-        <v>738</v>
+        <v>3104.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>07/05</v>
+        <v>07/12</v>
       </c>
       <c r="B22">
-        <v>276</v>
+        <v>259.6666666666667</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22">
-        <v>276</v>
+        <v>779</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>07/06</v>
+        <v>07/13</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>244</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>488</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>07/07</v>
+        <v>07/14</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -737,91 +737,91 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>07/08</v>
+        <v>07/15</v>
       </c>
       <c r="B25">
-        <v>243.275</v>
+        <v>237.05</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
       <c r="D25">
-        <v>486.55</v>
+        <v>474.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>07/09</v>
+        <v>07/16</v>
       </c>
       <c r="B26">
-        <v>295.75</v>
+        <v>258.5</v>
       </c>
       <c r="C26">
         <v>3</v>
       </c>
       <c r="D26">
-        <v>887.25</v>
+        <v>775.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>07/10</v>
+        <v>07/17</v>
       </c>
       <c r="B27">
-        <v>314.14</v>
+        <v>381.5</v>
       </c>
       <c r="C27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>3141.4</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>07/11</v>
+        <v>07/18</v>
       </c>
       <c r="B28">
-        <v>310.46999999999997</v>
+        <v>396</v>
       </c>
       <c r="C28">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D28">
-        <v>3104.7</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>07/12</v>
+        <v>07/19</v>
       </c>
       <c r="B29">
-        <v>259.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>779</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>07/13</v>
+        <v>07/20</v>
       </c>
       <c r="B30">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>07/14</v>
+        <v>07/21</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -835,105 +835,105 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>07/15</v>
+        <v>07/22</v>
       </c>
       <c r="B32">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>07/16</v>
+        <v>07/23</v>
       </c>
       <c r="B33">
-        <v>259.5</v>
+        <v>329</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>519</v>
+        <v>329</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>07/17</v>
+        <v>07/24</v>
       </c>
       <c r="B34">
-        <v>374</v>
+        <v>406.5</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D34">
-        <v>2618</v>
+        <v>813</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>07/18</v>
+        <v>07/25</v>
       </c>
       <c r="B35">
-        <v>384.8333333333333</v>
+        <v>389</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D35">
-        <v>2309</v>
+        <v>778</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>07/19</v>
+        <v>07/26</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>254.25</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>07/20</v>
+        <v>07/27</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>07/21</v>
+        <v>07/28</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>168</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>07/22</v>
+        <v>07/29</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -947,91 +947,91 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>07/23</v>
+        <v>07/30</v>
       </c>
       <c r="B40">
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>07/24</v>
+        <v>07/31</v>
       </c>
       <c r="B41">
-        <v>406.5</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>07/25</v>
+        <v>08/01</v>
       </c>
       <c r="B42">
-        <v>389</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>07/26</v>
+        <v>08/02</v>
       </c>
       <c r="B43">
-        <v>254.25</v>
+        <v>302</v>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D43">
-        <v>1017</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>07/27</v>
+        <v>08/03</v>
       </c>
       <c r="B44">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>07/28</v>
+        <v>08/04</v>
       </c>
       <c r="B45">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>07/29</v>
+        <v>08/05</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1045,35 +1045,35 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>07/30</v>
+        <v>08/06</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>301</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>07/31</v>
+        <v>08/07</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>396</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>08/01</v>
+        <v>08/08</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>08/02</v>
+        <v>08/09</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1101,7 +1101,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>08/03</v>
+        <v>08/10</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>08/04</v>
+        <v>08/11</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1129,7 +1129,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>08/05</v>
+        <v>08/12</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>08/06</v>
+        <v>08/13</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>08/07</v>
+        <v>08/14</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1171,35 +1171,35 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>08/08</v>
+        <v>08/15</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>223.2</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>223.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>08/09</v>
+        <v>08/16</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>167.4</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>167.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>08/10</v>
+        <v>08/17</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1213,7 +1213,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>08/11</v>
+        <v>08/18</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1227,7 +1227,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>08/12</v>
+        <v>08/19</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>08/13</v>
+        <v>08/20</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>08/14</v>
+        <v>08/21</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1269,35 +1269,35 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>08/15</v>
+        <v>08/22</v>
       </c>
       <c r="B63">
-        <v>223.2</v>
+        <v>0</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>223.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>08/16</v>
+        <v>08/23</v>
       </c>
       <c r="B64">
-        <v>167.4</v>
+        <v>0</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>167.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>08/17</v>
+        <v>08/24</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>08/18</v>
+        <v>08/25</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>08/19</v>
+        <v>08/26</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1339,7 +1339,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>08/20</v>
+        <v>08/27</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>08/21</v>
+        <v>08/28</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1367,7 +1367,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>08/22</v>
+        <v>08/29</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>08/23</v>
+        <v>08/30</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>08/24</v>
+        <v>08/31</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>08/25</v>
+        <v>09/01</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>08/26</v>
+        <v>09/02</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>08/27</v>
+        <v>09/03</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>08/28</v>
+        <v>09/04</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>08/29</v>
+        <v>09/05</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>08/30</v>
+        <v>09/06</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1493,35 +1493,35 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>08/31</v>
+        <v>09/07</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>208.8</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>208.8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>09/01</v>
+        <v>09/08</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>211.5</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>211.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>09/02</v>
+        <v>09/09</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>09/03</v>
+        <v>09/10</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>09/04</v>
+        <v>09/11</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>09/05</v>
+        <v>09/12</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1577,7 +1577,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>09/06</v>
+        <v>09/13</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>09/07</v>
+        <v>09/14</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>09/08</v>
+        <v>09/15</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>09/09</v>
+        <v>09/16</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>09/10</v>
+        <v>09/17</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1647,7 +1647,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>09/11</v>
+        <v>09/18</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1661,7 +1661,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>09/12</v>
+        <v>09/19</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>09/13</v>
+        <v>09/20</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>09/14</v>
+        <v>09/21</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>09/15</v>
+        <v>09/22</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>09/16</v>
+        <v>09/23</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>09/17</v>
+        <v>09/24</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1745,35 +1745,35 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>09/18</v>
+        <v>09/25</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>262.5</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>09/19</v>
+        <v>09/26</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>262.5</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>09/20</v>
+        <v>09/27</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>09/21</v>
+        <v>09/28</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>09/22</v>
+        <v>09/29</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>09/23</v>
+        <v>09/30</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,7 +1829,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>09/24</v>
+        <v>10/01</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1843,35 +1843,35 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>09/25</v>
+        <v>10/02</v>
       </c>
       <c r="B104">
-        <v>262.5</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>1050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>09/26</v>
+        <v>10/03</v>
       </c>
       <c r="B105">
-        <v>262.5</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>1050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>09/27</v>
+        <v>10/04</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>09/28</v>
+        <v>10/05</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>09/29</v>
+        <v>10/06</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>09/30</v>
+        <v>10/07</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>10/01</v>
+        <v>10/08</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>10/02</v>
+        <v>10/09</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>10/03</v>
+        <v>10/10</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>10/04</v>
+        <v>10/11</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>10/05</v>
+        <v>10/12</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>10/06</v>
+        <v>10/13</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>10/07</v>
+        <v>10/14</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>10/08</v>
+        <v>10/15</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>10/09</v>
+        <v>10/16</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>10/10</v>
+        <v>10/17</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>10/11</v>
+        <v>10/18</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>10/12</v>
+        <v>10/19</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>10/13</v>
+        <v>10/20</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>10/14</v>
+        <v>10/21</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>10/15</v>
+        <v>10/22</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>10/16</v>
+        <v>10/23</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -2151,7 +2151,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>10/17</v>
+        <v>10/24</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>10/18</v>
+        <v>10/25</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>10/19</v>
+        <v>10/26</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>10/20</v>
+        <v>10/27</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -2207,7 +2207,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>10/21</v>
+        <v>10/28</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>10/22</v>
+        <v>10/29</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>10/23</v>
+        <v>10/30</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>10/24</v>
+        <v>10/31</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -2263,7 +2263,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>10/25</v>
+        <v>11/01</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>10/26</v>
+        <v>11/02</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -2291,7 +2291,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>10/27</v>
+        <v>11/03</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>10/28</v>
+        <v>11/04</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>10/29</v>
+        <v>11/05</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>10/30</v>
+        <v>11/06</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>10/31</v>
+        <v>11/07</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>11/01</v>
+        <v>11/08</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -2375,7 +2375,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>11/02</v>
+        <v>11/09</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -2389,7 +2389,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>11/03</v>
+        <v>11/10</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -2403,7 +2403,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>11/04</v>
+        <v>11/11</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>11/05</v>
+        <v>11/12</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -2431,35 +2431,35 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>11/06</v>
+        <v>11/13</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>384.5</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>769</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>11/07</v>
+        <v>11/14</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>400.5</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>801</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>11/08</v>
+        <v>11/15</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -2473,7 +2473,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>11/09</v>
+        <v>11/16</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>11/10</v>
+        <v>11/17</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -2501,7 +2501,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>11/11</v>
+        <v>11/18</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -2515,7 +2515,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>11/12</v>
+        <v>11/19</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -2529,35 +2529,35 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>11/13</v>
+        <v>11/20</v>
       </c>
       <c r="B153">
-        <v>384.5</v>
+        <v>0</v>
       </c>
       <c r="C153">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D153">
-        <v>769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>11/14</v>
+        <v>11/21</v>
       </c>
       <c r="B154">
-        <v>400.5</v>
+        <v>0</v>
       </c>
       <c r="C154">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D154">
-        <v>801</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>11/15</v>
+        <v>11/22</v>
       </c>
       <c r="B155">
         <v>0</v>

--- a/ok-fc_occupancy_pace_150day.xlsx
+++ b/ok-fc_occupancy_pace_150day.xlsx
@@ -415,217 +415,217 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>06/22</v>
+        <v>06/29</v>
       </c>
       <c r="B2">
-        <v>220.18</v>
+        <v>243.275</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>1100.9</v>
+        <v>973.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>06/23</v>
+        <v>06/30</v>
       </c>
       <c r="B3">
-        <v>207.88333333333333</v>
+        <v>255.03333333333333</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>1247.3</v>
+        <v>765.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>06/24</v>
+        <v>07/01</v>
       </c>
       <c r="B4">
-        <v>223.1</v>
+        <v>299</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>1115.5</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>06/25</v>
+        <v>07/02</v>
       </c>
       <c r="B5">
-        <v>322</v>
+        <v>330.75</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>06/26</v>
+        <v>07/03</v>
       </c>
       <c r="B6">
-        <v>293.86666666666673</v>
+        <v>324.6</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>1763.2000000000003</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>06/27</v>
+        <v>07/04</v>
       </c>
       <c r="B7">
-        <v>283.14285714285717</v>
+        <v>328.6909090909091</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>1982</v>
+        <v>3615.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>06/28</v>
+        <v>07/05</v>
       </c>
       <c r="B8">
-        <v>297.5</v>
+        <v>233.66666666666666</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>595</v>
+        <v>701</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>06/29</v>
+        <v>07/06</v>
       </c>
       <c r="B9">
-        <v>288</v>
+        <v>254</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9">
-        <v>576</v>
+        <v>508</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>06/30</v>
+        <v>07/07</v>
       </c>
       <c r="B10">
-        <v>279.5</v>
+        <v>299</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>559</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>07/01</v>
+        <v>07/08</v>
       </c>
       <c r="B11">
-        <v>299</v>
+        <v>260.18333333333334</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>299</v>
+        <v>780.55</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>07/02</v>
+        <v>07/09</v>
       </c>
       <c r="B12">
-        <v>371.3333333333333</v>
+        <v>295.75</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
       <c r="D12">
-        <v>1114</v>
+        <v>887.25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>07/03</v>
+        <v>07/10</v>
       </c>
       <c r="B13">
-        <v>399</v>
+        <v>317.1272727272727</v>
       </c>
       <c r="C13">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D13">
-        <v>1197</v>
+        <v>3488.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>07/04</v>
+        <v>07/11</v>
       </c>
       <c r="B14">
-        <v>398.3333333333333</v>
+        <v>308.14166666666665</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D14">
-        <v>1195</v>
+        <v>3697.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>07/05</v>
+        <v>07/12</v>
       </c>
       <c r="B15">
-        <v>246</v>
+        <v>234.5</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15">
-        <v>492</v>
+        <v>938</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>07/06</v>
+        <v>07/13</v>
       </c>
       <c r="B16">
-        <v>197</v>
+        <v>219.95666666666668</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16">
-        <v>197</v>
+        <v>659.87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>07/07</v>
+        <v>07/14</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -639,301 +639,301 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>07/08</v>
+        <v>07/15</v>
       </c>
       <c r="B18">
-        <v>243.275</v>
+        <v>237.05</v>
       </c>
       <c r="C18">
         <v>2</v>
       </c>
       <c r="D18">
-        <v>486.55</v>
+        <v>474.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>07/09</v>
+        <v>07/16</v>
       </c>
       <c r="B19">
-        <v>295.75</v>
+        <v>258.5</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
       <c r="D19">
-        <v>887.25</v>
+        <v>775.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>07/10</v>
+        <v>07/17</v>
       </c>
       <c r="B20">
-        <v>314.14</v>
+        <v>381.5</v>
       </c>
       <c r="C20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>3141.3999999999996</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>07/11</v>
+        <v>07/18</v>
       </c>
       <c r="B21">
-        <v>310.46999999999997</v>
+        <v>396</v>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D21">
-        <v>3104.7</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>07/12</v>
+        <v>07/19</v>
       </c>
       <c r="B22">
-        <v>259.6666666666667</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>779</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>07/13</v>
+        <v>07/20</v>
       </c>
       <c r="B23">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>07/14</v>
+        <v>07/21</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>07/15</v>
+        <v>07/22</v>
       </c>
       <c r="B25">
-        <v>237.05</v>
+        <v>179</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>474.1</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>07/16</v>
+        <v>07/23</v>
       </c>
       <c r="B26">
-        <v>258.5</v>
+        <v>329</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>775.5</v>
+        <v>329</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>07/17</v>
+        <v>07/24</v>
       </c>
       <c r="B27">
-        <v>381.5</v>
+        <v>406.5</v>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>2289</v>
+        <v>813</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>07/18</v>
+        <v>07/25</v>
       </c>
       <c r="B28">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D28">
-        <v>1980</v>
+        <v>778</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>07/19</v>
+        <v>07/26</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>254.25</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>07/20</v>
+        <v>07/27</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>170.5</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>341</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>07/21</v>
+        <v>07/28</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>173.5</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>347</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>07/22</v>
+        <v>07/29</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>231</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>07/23</v>
+        <v>07/30</v>
       </c>
       <c r="B33">
-        <v>329</v>
+        <v>250</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33">
-        <v>329</v>
+        <v>250</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>07/24</v>
+        <v>07/31</v>
       </c>
       <c r="B34">
-        <v>406.5</v>
+        <v>264.5</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
       <c r="D34">
-        <v>813</v>
+        <v>529</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>07/25</v>
+        <v>08/01</v>
       </c>
       <c r="B35">
-        <v>389</v>
+        <v>275</v>
       </c>
       <c r="C35">
         <v>2</v>
       </c>
       <c r="D35">
-        <v>778</v>
+        <v>550</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>07/26</v>
+        <v>08/02</v>
       </c>
       <c r="B36">
-        <v>254.25</v>
+        <v>302</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D36">
-        <v>1017</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>07/27</v>
+        <v>08/03</v>
       </c>
       <c r="B37">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>07/28</v>
+        <v>08/04</v>
       </c>
       <c r="B38">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>07/29</v>
+        <v>08/05</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -947,35 +947,35 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>07/30</v>
+        <v>08/06</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>07/31</v>
+        <v>08/07</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>396</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>08/01</v>
+        <v>08/08</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -989,21 +989,21 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>08/02</v>
+        <v>08/09</v>
       </c>
       <c r="B43">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>08/03</v>
+        <v>08/10</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>08/04</v>
+        <v>08/11</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>08/05</v>
+        <v>08/12</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1045,63 +1045,63 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>08/06</v>
+        <v>08/13</v>
       </c>
       <c r="B47">
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>301</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>08/07</v>
+        <v>08/14</v>
       </c>
       <c r="B48">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>396</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>08/08</v>
+        <v>08/15</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>223.2</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>223.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>08/09</v>
+        <v>08/16</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>167.4</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>167.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>08/10</v>
+        <v>08/17</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>08/11</v>
+        <v>08/18</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1129,7 +1129,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>08/12</v>
+        <v>08/19</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>08/13</v>
+        <v>08/20</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>08/14</v>
+        <v>08/21</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1171,35 +1171,35 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>08/15</v>
+        <v>08/22</v>
       </c>
       <c r="B56">
-        <v>223.2</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>223.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>08/16</v>
+        <v>08/23</v>
       </c>
       <c r="B57">
-        <v>167.4</v>
+        <v>161.1</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="D57">
-        <v>167.4</v>
+        <v>161.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>08/17</v>
+        <v>08/24</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1213,7 +1213,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>08/18</v>
+        <v>08/25</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1227,7 +1227,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>08/19</v>
+        <v>08/26</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>08/20</v>
+        <v>08/27</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>08/21</v>
+        <v>08/28</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1269,7 +1269,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>08/22</v>
+        <v>08/29</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1283,7 +1283,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>08/23</v>
+        <v>08/30</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>08/24</v>
+        <v>08/31</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>08/25</v>
+        <v>09/01</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>08/26</v>
+        <v>09/02</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1339,7 +1339,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>08/27</v>
+        <v>09/03</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>08/28</v>
+        <v>09/04</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1367,7 +1367,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>08/29</v>
+        <v>09/05</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>08/30</v>
+        <v>09/06</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1395,35 +1395,35 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>08/31</v>
+        <v>09/07</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>208.8</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>208.8</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>09/01</v>
+        <v>09/08</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>211.5</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>211.5</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>09/02</v>
+        <v>09/09</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>09/03</v>
+        <v>09/10</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>09/04</v>
+        <v>09/11</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>09/05</v>
+        <v>09/12</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>09/06</v>
+        <v>09/13</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1493,35 +1493,35 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>09/07</v>
+        <v>09/14</v>
       </c>
       <c r="B79">
-        <v>208.8</v>
+        <v>0</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>208.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>09/08</v>
+        <v>09/15</v>
       </c>
       <c r="B80">
-        <v>211.5</v>
+        <v>0</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80">
-        <v>211.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>09/09</v>
+        <v>09/16</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>09/10</v>
+        <v>09/17</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>09/11</v>
+        <v>09/18</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>09/12</v>
+        <v>09/19</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1577,7 +1577,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>09/13</v>
+        <v>09/20</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>09/14</v>
+        <v>09/21</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>09/15</v>
+        <v>09/22</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>09/16</v>
+        <v>09/23</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>09/17</v>
+        <v>09/24</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1647,35 +1647,35 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>09/18</v>
+        <v>09/25</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>262.5</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>09/19</v>
+        <v>09/26</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>262.5</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>09/20</v>
+        <v>09/27</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>09/21</v>
+        <v>09/28</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>09/22</v>
+        <v>09/29</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>09/23</v>
+        <v>09/30</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>09/24</v>
+        <v>10/01</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1745,35 +1745,35 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>09/25</v>
+        <v>10/02</v>
       </c>
       <c r="B97">
-        <v>262.5</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>1050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>09/26</v>
+        <v>10/03</v>
       </c>
       <c r="B98">
-        <v>262.5</v>
+        <v>0</v>
       </c>
       <c r="C98">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D98">
-        <v>1050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>09/27</v>
+        <v>10/04</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>09/28</v>
+        <v>10/05</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>09/29</v>
+        <v>10/06</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>09/30</v>
+        <v>10/07</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,7 +1829,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>10/01</v>
+        <v>10/08</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>10/02</v>
+        <v>10/09</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>10/03</v>
+        <v>10/10</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1871,7 +1871,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>10/04</v>
+        <v>10/11</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>10/05</v>
+        <v>10/12</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>10/06</v>
+        <v>10/13</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>10/07</v>
+        <v>10/14</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>10/08</v>
+        <v>10/15</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>10/09</v>
+        <v>10/16</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>10/10</v>
+        <v>10/17</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>10/11</v>
+        <v>10/18</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>10/12</v>
+        <v>10/19</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>10/13</v>
+        <v>10/20</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>10/14</v>
+        <v>10/21</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>10/15</v>
+        <v>10/22</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>10/16</v>
+        <v>10/23</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>10/17</v>
+        <v>10/24</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>10/18</v>
+        <v>10/25</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>10/19</v>
+        <v>10/26</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>10/20</v>
+        <v>10/27</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>10/21</v>
+        <v>10/28</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>10/22</v>
+        <v>10/29</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>10/23</v>
+        <v>10/30</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -2151,7 +2151,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>10/24</v>
+        <v>10/31</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>10/25</v>
+        <v>11/01</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>10/26</v>
+        <v>11/02</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>10/27</v>
+        <v>11/03</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -2207,7 +2207,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>10/28</v>
+        <v>11/04</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>10/29</v>
+        <v>11/05</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>10/30</v>
+        <v>11/06</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>10/31</v>
+        <v>11/07</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -2263,7 +2263,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>11/01</v>
+        <v>11/08</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>11/02</v>
+        <v>11/09</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -2291,7 +2291,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>11/03</v>
+        <v>11/10</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>11/04</v>
+        <v>11/11</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>11/05</v>
+        <v>11/12</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -2333,35 +2333,35 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>11/06</v>
+        <v>11/13</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>384.5</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>769</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>11/07</v>
+        <v>11/14</v>
       </c>
       <c r="B140">
-        <v>0</v>
+        <v>400.5</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>801</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>11/08</v>
+        <v>11/15</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -2375,7 +2375,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>11/09</v>
+        <v>11/16</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -2389,7 +2389,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>11/10</v>
+        <v>11/17</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -2403,7 +2403,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>11/11</v>
+        <v>11/18</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>11/12</v>
+        <v>11/19</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -2431,35 +2431,35 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>11/13</v>
+        <v>11/20</v>
       </c>
       <c r="B146">
-        <v>384.5</v>
+        <v>0</v>
       </c>
       <c r="C146">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D146">
-        <v>769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>11/14</v>
+        <v>11/21</v>
       </c>
       <c r="B147">
-        <v>400.5</v>
+        <v>0</v>
       </c>
       <c r="C147">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D147">
-        <v>801</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>11/15</v>
+        <v>11/22</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -2473,7 +2473,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>11/16</v>
+        <v>11/23</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>11/17</v>
+        <v>11/24</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -2501,7 +2501,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>11/18</v>
+        <v>11/25</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -2515,7 +2515,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>11/19</v>
+        <v>11/26</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>11/20</v>
+        <v>11/27</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>11/21</v>
+        <v>11/28</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -2557,7 +2557,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>11/22</v>
+        <v>11/29</v>
       </c>
       <c r="B155">
         <v>0</v>

--- a/ok-fc_occupancy_pace_150day.xlsx
+++ b/ok-fc_occupancy_pace_150day.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D155"/>
+  <dimension ref="A1:D127"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,497 +415,497 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>06/29</v>
+        <v>07/06</v>
       </c>
       <c r="B2">
-        <v>243.275</v>
+        <v>245.66666666666666</v>
       </c>
       <c r="C2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>973.1</v>
+        <v>737</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>06/30</v>
+        <v>07/07</v>
       </c>
       <c r="B3">
-        <v>255.03333333333333</v>
+        <v>239</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>765.1</v>
+        <v>478</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>07/01</v>
+        <v>07/08</v>
       </c>
       <c r="B4">
-        <v>299</v>
+        <v>260.18333333333334</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>299</v>
+        <v>780.55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>07/02</v>
+        <v>07/09</v>
       </c>
       <c r="B5">
-        <v>330.75</v>
+        <v>295.75</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>1323</v>
+        <v>887.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>07/03</v>
+        <v>07/10</v>
       </c>
       <c r="B6">
-        <v>324.6</v>
+        <v>317.1272727272727</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>3246</v>
+        <v>3488.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>07/04</v>
+        <v>07/11</v>
       </c>
       <c r="B7">
-        <v>328.6909090909091</v>
+        <v>308.14166666666665</v>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7">
-        <v>3615.6</v>
+        <v>3697.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>07/05</v>
+        <v>07/12</v>
       </c>
       <c r="B8">
-        <v>233.66666666666666</v>
+        <v>230.875</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D8">
-        <v>701</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>07/06</v>
+        <v>07/13</v>
       </c>
       <c r="B9">
-        <v>254</v>
+        <v>219.95666666666668</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>508</v>
+        <v>659.87</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>07/07</v>
+        <v>07/14</v>
       </c>
       <c r="B10">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>07/08</v>
+        <v>07/15</v>
       </c>
       <c r="B11">
-        <v>260.18333333333334</v>
+        <v>237.05</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>780.55</v>
+        <v>474.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>07/09</v>
+        <v>07/16</v>
       </c>
       <c r="B12">
-        <v>295.75</v>
+        <v>258.5</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
       <c r="D12">
-        <v>887.25</v>
+        <v>775.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>07/10</v>
+        <v>07/17</v>
       </c>
       <c r="B13">
-        <v>317.1272727272727</v>
+        <v>392</v>
       </c>
       <c r="C13">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D13">
-        <v>3488.4</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>07/11</v>
+        <v>07/18</v>
       </c>
       <c r="B14">
-        <v>308.14166666666665</v>
+        <v>412.75</v>
       </c>
       <c r="C14">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>3697.7</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>07/12</v>
+        <v>07/19</v>
       </c>
       <c r="B15">
-        <v>234.5</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>938</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>07/13</v>
+        <v>07/20</v>
       </c>
       <c r="B16">
-        <v>219.95666666666668</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>659.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>07/14</v>
+        <v>07/21</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>07/15</v>
+        <v>07/22</v>
       </c>
       <c r="B18">
-        <v>237.05</v>
+        <v>179</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>474.1</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>07/16</v>
+        <v>07/23</v>
       </c>
       <c r="B19">
-        <v>258.5</v>
+        <v>329</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>775.5</v>
+        <v>329</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>07/17</v>
+        <v>07/24</v>
       </c>
       <c r="B20">
-        <v>381.5</v>
+        <v>386</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20">
-        <v>2289</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>07/18</v>
+        <v>07/25</v>
       </c>
       <c r="B21">
-        <v>396</v>
+        <v>361.5</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D21">
-        <v>1980</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>07/19</v>
+        <v>07/26</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>254.25</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>07/20</v>
+        <v>07/27</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>170.5</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>341</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>07/21</v>
+        <v>07/28</v>
       </c>
       <c r="B24">
-        <v>179</v>
+        <v>207.125</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D24">
-        <v>179</v>
+        <v>828.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>07/22</v>
+        <v>07/29</v>
       </c>
       <c r="B25">
-        <v>179</v>
+        <v>246.79999999999998</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25">
-        <v>179</v>
+        <v>740.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>07/23</v>
+        <v>07/30</v>
       </c>
       <c r="B26">
-        <v>329</v>
+        <v>287.5</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26">
-        <v>329</v>
+        <v>575</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>07/24</v>
+        <v>07/31</v>
       </c>
       <c r="B27">
-        <v>406.5</v>
+        <v>301</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27">
-        <v>813</v>
+        <v>903</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>07/25</v>
+        <v>08/01</v>
       </c>
       <c r="B28">
-        <v>389</v>
+        <v>275</v>
       </c>
       <c r="C28">
         <v>2</v>
       </c>
       <c r="D28">
-        <v>778</v>
+        <v>550</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>07/26</v>
+        <v>08/02</v>
       </c>
       <c r="B29">
-        <v>254.25</v>
+        <v>302</v>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>1017</v>
+        <v>302</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>07/27</v>
+        <v>08/03</v>
       </c>
       <c r="B30">
-        <v>170.5</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>341</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>07/28</v>
+        <v>08/04</v>
       </c>
       <c r="B31">
-        <v>173.5</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>347</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>07/29</v>
+        <v>08/05</v>
       </c>
       <c r="B32">
-        <v>231</v>
+        <v>271.49</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32">
-        <v>231</v>
+        <v>271.49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>07/30</v>
+        <v>08/06</v>
       </c>
       <c r="B33">
-        <v>250</v>
+        <v>301</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33">
-        <v>250</v>
+        <v>301</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>07/31</v>
+        <v>08/07</v>
       </c>
       <c r="B34">
-        <v>264.5</v>
+        <v>374</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
       <c r="D34">
-        <v>529</v>
+        <v>748</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>08/01</v>
+        <v>08/08</v>
       </c>
       <c r="B35">
-        <v>275</v>
+        <v>344</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>550</v>
+        <v>344</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>08/02</v>
+        <v>08/09</v>
       </c>
       <c r="B36">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>08/03</v>
+        <v>08/10</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -919,7 +919,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>08/04</v>
+        <v>08/11</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -933,7 +933,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>08/05</v>
+        <v>08/12</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -947,63 +947,63 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>08/06</v>
+        <v>08/13</v>
       </c>
       <c r="B40">
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>301</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>08/07</v>
+        <v>08/14</v>
       </c>
       <c r="B41">
-        <v>396</v>
+        <v>298</v>
       </c>
       <c r="C41">
         <v>1</v>
       </c>
       <c r="D41">
-        <v>396</v>
+        <v>298</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>08/08</v>
+        <v>08/15</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>253.6</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>507.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>08/09</v>
+        <v>08/16</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>167.4</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>167.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>08/10</v>
+        <v>08/17</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>08/11</v>
+        <v>08/18</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>08/12</v>
+        <v>08/19</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>08/13</v>
+        <v>08/20</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>08/14</v>
+        <v>08/21</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1073,35 +1073,35 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>08/15</v>
+        <v>08/22</v>
       </c>
       <c r="B49">
-        <v>223.2</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>223.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>08/16</v>
+        <v>08/23</v>
       </c>
       <c r="B50">
-        <v>167.4</v>
+        <v>161.1</v>
       </c>
       <c r="C50">
         <v>1</v>
       </c>
       <c r="D50">
-        <v>167.4</v>
+        <v>161.1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>08/17</v>
+        <v>08/24</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>08/18</v>
+        <v>08/25</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1129,7 +1129,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>08/19</v>
+        <v>08/26</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>08/20</v>
+        <v>08/27</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>08/21</v>
+        <v>08/28</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>08/22</v>
+        <v>08/29</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1185,21 +1185,21 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>08/23</v>
+        <v>08/30</v>
       </c>
       <c r="B57">
-        <v>161.1</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>161.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>08/24</v>
+        <v>08/31</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1213,7 +1213,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>08/25</v>
+        <v>09/01</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1227,7 +1227,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>08/26</v>
+        <v>09/02</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>08/27</v>
+        <v>09/03</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1255,77 +1255,77 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>08/28</v>
+        <v>09/04</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>460</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>08/29</v>
+        <v>09/05</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>438</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>08/30</v>
+        <v>09/06</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>438</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>08/31</v>
+        <v>09/07</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>208.8</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>208.8</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>09/01</v>
+        <v>09/08</v>
       </c>
       <c r="B66">
-        <v>0</v>
+        <v>211.5</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>211.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>09/02</v>
+        <v>09/09</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1339,7 +1339,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>09/03</v>
+        <v>09/10</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>09/04</v>
+        <v>09/11</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1367,7 +1367,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>09/05</v>
+        <v>09/12</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>09/06</v>
+        <v>09/13</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1395,35 +1395,35 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>09/07</v>
+        <v>09/14</v>
       </c>
       <c r="B72">
-        <v>208.8</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>208.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>09/08</v>
+        <v>09/15</v>
       </c>
       <c r="B73">
-        <v>211.5</v>
+        <v>0</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>211.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>09/09</v>
+        <v>09/16</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>09/10</v>
+        <v>09/17</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>09/11</v>
+        <v>09/18</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>09/12</v>
+        <v>09/19</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>09/13</v>
+        <v>09/20</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1493,7 +1493,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>09/14</v>
+        <v>09/21</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1507,7 +1507,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>09/15</v>
+        <v>09/22</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>09/16</v>
+        <v>09/23</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>09/17</v>
+        <v>09/24</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1549,35 +1549,35 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>09/18</v>
+        <v>09/25</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>262.5</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>09/19</v>
+        <v>09/26</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>262.5</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>09/20</v>
+        <v>09/27</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>09/21</v>
+        <v>09/28</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>09/22</v>
+        <v>09/29</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>09/23</v>
+        <v>09/30</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>09/24</v>
+        <v>10/01</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1647,35 +1647,35 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>09/25</v>
+        <v>10/02</v>
       </c>
       <c r="B90">
-        <v>262.5</v>
+        <v>0</v>
       </c>
       <c r="C90">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>1050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>09/26</v>
+        <v>10/03</v>
       </c>
       <c r="B91">
-        <v>262.5</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>1050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>09/27</v>
+        <v>10/04</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>09/28</v>
+        <v>10/05</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>09/29</v>
+        <v>10/06</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>09/30</v>
+        <v>10/07</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>10/01</v>
+        <v>10/08</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>10/02</v>
+        <v>10/09</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>10/03</v>
+        <v>10/10</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>10/04</v>
+        <v>10/11</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>10/05</v>
+        <v>10/12</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>10/06</v>
+        <v>10/13</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>10/07</v>
+        <v>10/14</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,35 +1829,35 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>10/08</v>
+        <v>10/15</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>356</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>10/09</v>
+        <v>10/16</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>443</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>10/10</v>
+        <v>10/17</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1871,7 +1871,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>10/11</v>
+        <v>10/18</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>10/12</v>
+        <v>10/19</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>10/13</v>
+        <v>10/20</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>10/14</v>
+        <v>10/21</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>10/15</v>
+        <v>10/22</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>10/16</v>
+        <v>10/23</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>10/17</v>
+        <v>10/24</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>10/18</v>
+        <v>10/25</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>10/19</v>
+        <v>10/26</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>10/20</v>
+        <v>10/27</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>10/21</v>
+        <v>10/28</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>10/22</v>
+        <v>10/29</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>10/23</v>
+        <v>10/30</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>10/24</v>
+        <v>10/31</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>10/25</v>
+        <v>11/01</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>10/26</v>
+        <v>11/02</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>10/27</v>
+        <v>11/03</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>10/28</v>
+        <v>11/04</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>10/29</v>
+        <v>11/05</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>10/30</v>
+        <v>11/06</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -2151,7 +2151,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>10/31</v>
+        <v>11/07</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>11/01</v>
+        <v>11/08</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -2174,404 +2174,12 @@
         <v>0</v>
       </c>
       <c r="D127">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v>11/02</v>
-      </c>
-      <c r="B128">
-        <v>0</v>
-      </c>
-      <c r="C128">
-        <v>0</v>
-      </c>
-      <c r="D128">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>11/03</v>
-      </c>
-      <c r="B129">
-        <v>0</v>
-      </c>
-      <c r="C129">
-        <v>0</v>
-      </c>
-      <c r="D129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v>11/04</v>
-      </c>
-      <c r="B130">
-        <v>0</v>
-      </c>
-      <c r="C130">
-        <v>0</v>
-      </c>
-      <c r="D130">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="str">
-        <v>11/05</v>
-      </c>
-      <c r="B131">
-        <v>0</v>
-      </c>
-      <c r="C131">
-        <v>0</v>
-      </c>
-      <c r="D131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="str">
-        <v>11/06</v>
-      </c>
-      <c r="B132">
-        <v>0</v>
-      </c>
-      <c r="C132">
-        <v>0</v>
-      </c>
-      <c r="D132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>11/07</v>
-      </c>
-      <c r="B133">
-        <v>0</v>
-      </c>
-      <c r="C133">
-        <v>0</v>
-      </c>
-      <c r="D133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="str">
-        <v>11/08</v>
-      </c>
-      <c r="B134">
-        <v>0</v>
-      </c>
-      <c r="C134">
-        <v>0</v>
-      </c>
-      <c r="D134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v>11/09</v>
-      </c>
-      <c r="B135">
-        <v>0</v>
-      </c>
-      <c r="C135">
-        <v>0</v>
-      </c>
-      <c r="D135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="str">
-        <v>11/10</v>
-      </c>
-      <c r="B136">
-        <v>0</v>
-      </c>
-      <c r="C136">
-        <v>0</v>
-      </c>
-      <c r="D136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v>11/11</v>
-      </c>
-      <c r="B137">
-        <v>0</v>
-      </c>
-      <c r="C137">
-        <v>0</v>
-      </c>
-      <c r="D137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>11/12</v>
-      </c>
-      <c r="B138">
-        <v>0</v>
-      </c>
-      <c r="C138">
-        <v>0</v>
-      </c>
-      <c r="D138">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v>11/13</v>
-      </c>
-      <c r="B139">
-        <v>384.5</v>
-      </c>
-      <c r="C139">
-        <v>2</v>
-      </c>
-      <c r="D139">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="str">
-        <v>11/14</v>
-      </c>
-      <c r="B140">
-        <v>400.5</v>
-      </c>
-      <c r="C140">
-        <v>2</v>
-      </c>
-      <c r="D140">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="str">
-        <v>11/15</v>
-      </c>
-      <c r="B141">
-        <v>0</v>
-      </c>
-      <c r="C141">
-        <v>0</v>
-      </c>
-      <c r="D141">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="str">
-        <v>11/16</v>
-      </c>
-      <c r="B142">
-        <v>0</v>
-      </c>
-      <c r="C142">
-        <v>0</v>
-      </c>
-      <c r="D142">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="str">
-        <v>11/17</v>
-      </c>
-      <c r="B143">
-        <v>0</v>
-      </c>
-      <c r="C143">
-        <v>0</v>
-      </c>
-      <c r="D143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="str">
-        <v>11/18</v>
-      </c>
-      <c r="B144">
-        <v>0</v>
-      </c>
-      <c r="C144">
-        <v>0</v>
-      </c>
-      <c r="D144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v>11/19</v>
-      </c>
-      <c r="B145">
-        <v>0</v>
-      </c>
-      <c r="C145">
-        <v>0</v>
-      </c>
-      <c r="D145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="str">
-        <v>11/20</v>
-      </c>
-      <c r="B146">
-        <v>0</v>
-      </c>
-      <c r="C146">
-        <v>0</v>
-      </c>
-      <c r="D146">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="str">
-        <v>11/21</v>
-      </c>
-      <c r="B147">
-        <v>0</v>
-      </c>
-      <c r="C147">
-        <v>0</v>
-      </c>
-      <c r="D147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="str">
-        <v>11/22</v>
-      </c>
-      <c r="B148">
-        <v>0</v>
-      </c>
-      <c r="C148">
-        <v>0</v>
-      </c>
-      <c r="D148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="str">
-        <v>11/23</v>
-      </c>
-      <c r="B149">
-        <v>0</v>
-      </c>
-      <c r="C149">
-        <v>0</v>
-      </c>
-      <c r="D149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="str">
-        <v>11/24</v>
-      </c>
-      <c r="B150">
-        <v>0</v>
-      </c>
-      <c r="C150">
-        <v>0</v>
-      </c>
-      <c r="D150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
-        <v>11/25</v>
-      </c>
-      <c r="B151">
-        <v>0</v>
-      </c>
-      <c r="C151">
-        <v>0</v>
-      </c>
-      <c r="D151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="str">
-        <v>11/26</v>
-      </c>
-      <c r="B152">
-        <v>0</v>
-      </c>
-      <c r="C152">
-        <v>0</v>
-      </c>
-      <c r="D152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
-        <v>11/27</v>
-      </c>
-      <c r="B153">
-        <v>0</v>
-      </c>
-      <c r="C153">
-        <v>0</v>
-      </c>
-      <c r="D153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="str">
-        <v>11/28</v>
-      </c>
-      <c r="B154">
-        <v>0</v>
-      </c>
-      <c r="C154">
-        <v>0</v>
-      </c>
-      <c r="D154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="str">
-        <v>11/29</v>
-      </c>
-      <c r="B155">
-        <v>0</v>
-      </c>
-      <c r="C155">
-        <v>0</v>
-      </c>
-      <c r="D155">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D155"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D127"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ok-fc_occupancy_pace_150day.xlsx
+++ b/ok-fc_occupancy_pace_150day.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D127"/>
+  <dimension ref="A1:D154"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,399 +415,399 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>07/06</v>
+        <v>07/13</v>
       </c>
       <c r="B2">
-        <v>245.66666666666666</v>
+        <v>195.10875</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D2">
-        <v>737</v>
+        <v>1560.87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>07/07</v>
+        <v>07/14</v>
       </c>
       <c r="B3">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>478</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>07/08</v>
+        <v>07/15</v>
       </c>
       <c r="B4">
-        <v>260.18333333333334</v>
+        <v>244.5</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>780.55</v>
+        <v>489</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>07/09</v>
+        <v>07/16</v>
       </c>
       <c r="B5">
-        <v>295.75</v>
+        <v>221.2</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>887.25</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>07/10</v>
+        <v>07/17</v>
       </c>
       <c r="B6">
-        <v>317.1272727272727</v>
+        <v>322</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>3488.4</v>
+        <v>2898</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>07/11</v>
+        <v>07/18</v>
       </c>
       <c r="B7">
-        <v>308.14166666666665</v>
+        <v>375.2</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>3697.7</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>07/12</v>
+        <v>07/19</v>
       </c>
       <c r="B8">
-        <v>230.875</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1847</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>07/13</v>
+        <v>07/20</v>
       </c>
       <c r="B9">
-        <v>219.95666666666668</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>659.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>07/14</v>
+        <v>07/21</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>07/15</v>
+        <v>07/22</v>
       </c>
       <c r="B11">
-        <v>237.05</v>
+        <v>179</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>474.1</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>07/16</v>
+        <v>07/23</v>
       </c>
       <c r="B12">
-        <v>258.5</v>
+        <v>329</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>775.5</v>
+        <v>329</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>07/17</v>
+        <v>07/24</v>
       </c>
       <c r="B13">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13">
-        <v>1960</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>07/18</v>
+        <v>07/25</v>
       </c>
       <c r="B14">
-        <v>412.75</v>
+        <v>361.5</v>
       </c>
       <c r="C14">
         <v>4</v>
       </c>
       <c r="D14">
-        <v>1651</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>07/19</v>
+        <v>07/26</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>258.8</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>07/20</v>
+        <v>07/27</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>199.66666666666666</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>599</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>07/21</v>
+        <v>07/28</v>
       </c>
       <c r="B17">
-        <v>179</v>
+        <v>207.125</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>179</v>
+        <v>828.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>07/22</v>
+        <v>07/29</v>
       </c>
       <c r="B18">
-        <v>179</v>
+        <v>250.1</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18">
-        <v>179</v>
+        <v>1000.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>07/23</v>
+        <v>07/30</v>
       </c>
       <c r="B19">
-        <v>329</v>
+        <v>285.5</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D19">
-        <v>329</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>07/24</v>
+        <v>07/31</v>
       </c>
       <c r="B20">
-        <v>386</v>
+        <v>307.3</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D20">
-        <v>1544</v>
+        <v>2458.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>07/25</v>
+        <v>08/01</v>
       </c>
       <c r="B21">
-        <v>361.5</v>
+        <v>301.86</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21">
-        <v>1446</v>
+        <v>1509.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>07/26</v>
+        <v>08/02</v>
       </c>
       <c r="B22">
-        <v>254.25</v>
+        <v>302</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>1017</v>
+        <v>302</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>07/27</v>
+        <v>08/03</v>
       </c>
       <c r="B23">
-        <v>170.5</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>341</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>07/28</v>
+        <v>08/04</v>
       </c>
       <c r="B24">
-        <v>207.125</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>828.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>07/29</v>
+        <v>08/05</v>
       </c>
       <c r="B25">
-        <v>246.79999999999998</v>
+        <v>271.49</v>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>740.4</v>
+        <v>271.49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>07/30</v>
+        <v>08/06</v>
       </c>
       <c r="B26">
-        <v>287.5</v>
+        <v>298.55</v>
       </c>
       <c r="C26">
         <v>2</v>
       </c>
       <c r="D26">
-        <v>575</v>
+        <v>597.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>07/31</v>
+        <v>08/07</v>
       </c>
       <c r="B27">
-        <v>301</v>
+        <v>354.65</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27">
-        <v>903</v>
+        <v>1418.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>08/01</v>
+        <v>08/08</v>
       </c>
       <c r="B28">
-        <v>275</v>
+        <v>336.6333333333333</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28">
-        <v>550</v>
+        <v>1009.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>08/02</v>
+        <v>08/09</v>
       </c>
       <c r="B29">
-        <v>302</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>302</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>08/03</v>
+        <v>08/10</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -821,7 +821,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>08/04</v>
+        <v>08/11</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -835,77 +835,77 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>08/05</v>
+        <v>08/12</v>
       </c>
       <c r="B32">
-        <v>271.49</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>271.49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>08/06</v>
+        <v>08/13</v>
       </c>
       <c r="B33">
-        <v>301</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>301</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>08/07</v>
+        <v>08/14</v>
       </c>
       <c r="B34">
-        <v>374</v>
+        <v>328.5</v>
       </c>
       <c r="C34">
         <v>2</v>
       </c>
       <c r="D34">
-        <v>748</v>
+        <v>657</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>08/08</v>
+        <v>08/15</v>
       </c>
       <c r="B35">
-        <v>344</v>
+        <v>280.73333333333335</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D35">
-        <v>344</v>
+        <v>842.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>08/09</v>
+        <v>08/16</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>167.4</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>167.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>08/10</v>
+        <v>08/17</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -919,7 +919,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>08/11</v>
+        <v>08/18</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -933,7 +933,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>08/12</v>
+        <v>08/19</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -947,7 +947,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>08/13</v>
+        <v>08/20</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -961,49 +961,49 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>08/14</v>
+        <v>08/21</v>
       </c>
       <c r="B41">
-        <v>298</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>298</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>08/15</v>
+        <v>08/22</v>
       </c>
       <c r="B42">
-        <v>253.6</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>507.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>08/16</v>
+        <v>08/23</v>
       </c>
       <c r="B43">
-        <v>167.4</v>
+        <v>161.1</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="D43">
-        <v>167.4</v>
+        <v>161.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>08/17</v>
+        <v>08/24</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>08/18</v>
+        <v>08/25</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>08/19</v>
+        <v>08/26</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1045,7 +1045,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>08/20</v>
+        <v>08/27</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>08/21</v>
+        <v>08/28</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>08/22</v>
+        <v>08/29</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1087,21 +1087,21 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>08/23</v>
+        <v>08/30</v>
       </c>
       <c r="B50">
-        <v>161.1</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>161.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>08/24</v>
+        <v>08/31</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>08/25</v>
+        <v>09/01</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1129,119 +1129,119 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>08/26</v>
+        <v>09/02</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>215</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>08/27</v>
+        <v>09/03</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>226.5</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>453</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>08/28</v>
+        <v>09/04</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>460</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>08/29</v>
+        <v>09/05</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>438</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>08/30</v>
+        <v>09/06</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>438</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>438</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>08/31</v>
+        <v>09/07</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>209.9</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>419.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>09/01</v>
+        <v>09/08</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>213.25</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>426.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>09/02</v>
+        <v>09/09</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>217</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>09/03</v>
+        <v>09/10</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1255,77 +1255,77 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>09/04</v>
+        <v>09/11</v>
       </c>
       <c r="B62">
-        <v>460</v>
+        <v>0</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>460</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>09/05</v>
+        <v>09/12</v>
       </c>
       <c r="B63">
-        <v>438</v>
+        <v>0</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>438</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>09/06</v>
+        <v>09/13</v>
       </c>
       <c r="B64">
-        <v>438</v>
+        <v>0</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>438</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>09/07</v>
+        <v>09/14</v>
       </c>
       <c r="B65">
-        <v>208.8</v>
+        <v>0</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>208.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>09/08</v>
+        <v>09/15</v>
       </c>
       <c r="B66">
-        <v>211.5</v>
+        <v>0</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>211.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>09/09</v>
+        <v>09/16</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1339,7 +1339,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>09/10</v>
+        <v>09/17</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>09/11</v>
+        <v>09/18</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -1367,7 +1367,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>09/12</v>
+        <v>09/19</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>09/13</v>
+        <v>09/20</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>09/14</v>
+        <v>09/21</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>09/15</v>
+        <v>09/22</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>09/16</v>
+        <v>09/23</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>09/17</v>
+        <v>09/24</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1451,35 +1451,35 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>09/18</v>
+        <v>09/25</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>262.5</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>09/19</v>
+        <v>09/26</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>262.5</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>09/20</v>
+        <v>09/27</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1493,7 +1493,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>09/21</v>
+        <v>09/28</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1507,7 +1507,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>09/22</v>
+        <v>09/29</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>09/23</v>
+        <v>09/30</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>09/24</v>
+        <v>10/01</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1549,35 +1549,35 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>09/25</v>
+        <v>10/02</v>
       </c>
       <c r="B83">
-        <v>262.5</v>
+        <v>0</v>
       </c>
       <c r="C83">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>1050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>09/26</v>
+        <v>10/03</v>
       </c>
       <c r="B84">
-        <v>262.5</v>
+        <v>0</v>
       </c>
       <c r="C84">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D84">
-        <v>1050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>09/27</v>
+        <v>10/04</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>09/28</v>
+        <v>10/05</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>09/29</v>
+        <v>10/06</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>09/30</v>
+        <v>10/07</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>10/01</v>
+        <v>10/08</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1647,7 +1647,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>10/02</v>
+        <v>10/09</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1661,7 +1661,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>10/03</v>
+        <v>10/10</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>10/04</v>
+        <v>10/11</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>10/05</v>
+        <v>10/12</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>10/06</v>
+        <v>10/13</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>10/07</v>
+        <v>10/14</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1731,35 +1731,35 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>10/08</v>
+        <v>10/15</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>356</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>10/09</v>
+        <v>10/16</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>443</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>10/10</v>
+        <v>10/17</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>10/11</v>
+        <v>10/18</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>10/12</v>
+        <v>10/19</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>10/13</v>
+        <v>10/20</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>10/14</v>
+        <v>10/21</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,35 +1829,35 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>10/15</v>
+        <v>10/22</v>
       </c>
       <c r="B103">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D103">
-        <v>356</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>10/16</v>
+        <v>10/23</v>
       </c>
       <c r="B104">
-        <v>443</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>10/17</v>
+        <v>10/24</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1871,7 +1871,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>10/18</v>
+        <v>10/25</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>10/19</v>
+        <v>10/26</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>10/20</v>
+        <v>10/27</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>10/21</v>
+        <v>10/28</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>10/22</v>
+        <v>10/29</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>10/23</v>
+        <v>10/30</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>10/24</v>
+        <v>10/31</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>10/25</v>
+        <v>11/01</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>10/26</v>
+        <v>11/02</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>10/27</v>
+        <v>11/03</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>10/28</v>
+        <v>11/04</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>10/29</v>
+        <v>11/05</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>10/30</v>
+        <v>11/06</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>10/31</v>
+        <v>11/07</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>11/01</v>
+        <v>11/08</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>11/02</v>
+        <v>11/09</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>11/03</v>
+        <v>11/10</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>11/04</v>
+        <v>11/11</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>11/05</v>
+        <v>11/12</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -2137,35 +2137,35 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>11/06</v>
+        <v>11/13</v>
       </c>
       <c r="B125">
-        <v>0</v>
+        <v>367</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>367</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>11/07</v>
+        <v>11/14</v>
       </c>
       <c r="B126">
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>382</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>11/08</v>
+        <v>11/15</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -2174,12 +2174,390 @@
         <v>0</v>
       </c>
       <c r="D127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>11/16</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>11/17</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>11/18</v>
+      </c>
+      <c r="B130">
+        <v>0</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>11/19</v>
+      </c>
+      <c r="B131">
+        <v>0</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>11/20</v>
+      </c>
+      <c r="B132">
+        <v>0</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>11/21</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>11/22</v>
+      </c>
+      <c r="B134">
+        <v>0</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>11/23</v>
+      </c>
+      <c r="B135">
+        <v>0</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>11/24</v>
+      </c>
+      <c r="B136">
+        <v>0</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
+      <c r="D136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>11/25</v>
+      </c>
+      <c r="B137">
+        <v>0</v>
+      </c>
+      <c r="C137">
+        <v>0</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>11/26</v>
+      </c>
+      <c r="B138">
+        <v>0</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+      <c r="D138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>11/27</v>
+      </c>
+      <c r="B139">
+        <v>0</v>
+      </c>
+      <c r="C139">
+        <v>0</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>11/28</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+      <c r="C140">
+        <v>0</v>
+      </c>
+      <c r="D140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>11/29</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>11/30</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+      <c r="C142">
+        <v>0</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>12/01</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+      <c r="C143">
+        <v>0</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>12/02</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>12/03</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>12/04</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+      <c r="D146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>12/05</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+      <c r="D147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>12/06</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
+      <c r="D148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>12/07</v>
+      </c>
+      <c r="B149">
+        <v>0</v>
+      </c>
+      <c r="C149">
+        <v>0</v>
+      </c>
+      <c r="D149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>12/08</v>
+      </c>
+      <c r="B150">
+        <v>0</v>
+      </c>
+      <c r="C150">
+        <v>0</v>
+      </c>
+      <c r="D150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>12/09</v>
+      </c>
+      <c r="B151">
+        <v>0</v>
+      </c>
+      <c r="C151">
+        <v>0</v>
+      </c>
+      <c r="D151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>12/10</v>
+      </c>
+      <c r="B152">
+        <v>0</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
+      <c r="D152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>12/11</v>
+      </c>
+      <c r="B153">
+        <v>0</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+      <c r="D153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>12/12</v>
+      </c>
+      <c r="B154">
+        <v>0</v>
+      </c>
+      <c r="C154">
+        <v>0</v>
+      </c>
+      <c r="D154">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D127"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D154"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ok-fc_occupancy_pace_150day.xlsx
+++ b/ok-fc_occupancy_pace_150day.xlsx
@@ -415,315 +415,315 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>07/13</v>
+        <v>07/20</v>
       </c>
       <c r="B2">
-        <v>195.10875</v>
+        <v>166.62666666666667</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1560.87</v>
+        <v>499.88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>07/14</v>
+        <v>07/21</v>
       </c>
       <c r="B3">
-        <v>214</v>
+        <v>182.42999999999998</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>428</v>
+        <v>547.29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>07/15</v>
+        <v>07/22</v>
       </c>
       <c r="B4">
-        <v>244.5</v>
+        <v>191.25</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>489</v>
+        <v>573.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>07/16</v>
+        <v>07/23</v>
       </c>
       <c r="B5">
-        <v>221.2</v>
+        <v>263</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>1106</v>
+        <v>526</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>07/17</v>
+        <v>07/24</v>
       </c>
       <c r="B6">
-        <v>322</v>
+        <v>294.6644444444444</v>
       </c>
       <c r="C6">
         <v>9</v>
       </c>
       <c r="D6">
-        <v>2898</v>
+        <v>2651.98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>07/18</v>
+        <v>07/25</v>
       </c>
       <c r="B7">
-        <v>375.2</v>
+        <v>276.47555555555556</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>1876</v>
+        <v>2488.28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>07/19</v>
+        <v>07/26</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>242.4857142857143</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1697.4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>07/20</v>
+        <v>07/27</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>193.42000000000002</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>967.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>07/21</v>
+        <v>07/28</v>
       </c>
       <c r="B10">
-        <v>179</v>
+        <v>196.94285714285715</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D10">
-        <v>179</v>
+        <v>1378.6000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>07/22</v>
+        <v>07/29</v>
       </c>
       <c r="B11">
-        <v>179</v>
+        <v>239.08</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D11">
-        <v>179</v>
+        <v>1195.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>07/23</v>
+        <v>07/30</v>
       </c>
       <c r="B12">
-        <v>329</v>
+        <v>269</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D12">
-        <v>329</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>07/24</v>
+        <v>07/31</v>
       </c>
       <c r="B13">
-        <v>386</v>
+        <v>296.6</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D13">
-        <v>1544</v>
+        <v>2669.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>07/25</v>
+        <v>08/01</v>
       </c>
       <c r="B14">
-        <v>361.5</v>
+        <v>290.21666666666664</v>
       </c>
       <c r="C14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D14">
-        <v>1446</v>
+        <v>1741.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>07/26</v>
+        <v>08/02</v>
       </c>
       <c r="B15">
-        <v>258.8</v>
+        <v>259.2</v>
       </c>
       <c r="C15">
         <v>5</v>
       </c>
       <c r="D15">
-        <v>1294</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>07/27</v>
+        <v>08/03</v>
       </c>
       <c r="B16">
-        <v>199.66666666666666</v>
+        <v>236.8</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>599</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>07/28</v>
+        <v>08/04</v>
       </c>
       <c r="B17">
-        <v>207.125</v>
+        <v>259</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>828.5</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>07/29</v>
+        <v>08/05</v>
       </c>
       <c r="B18">
-        <v>250.1</v>
+        <v>265.245</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>1000.4</v>
+        <v>530.49</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>07/30</v>
+        <v>08/06</v>
       </c>
       <c r="B19">
-        <v>285.5</v>
+        <v>294.3666666666667</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19">
-        <v>1142</v>
+        <v>883.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>07/31</v>
+        <v>08/07</v>
       </c>
       <c r="B20">
-        <v>307.3</v>
+        <v>352.71999999999997</v>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>2458.4</v>
+        <v>1763.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>08/01</v>
+        <v>08/08</v>
       </c>
       <c r="B21">
-        <v>301.86</v>
+        <v>263.78000000000003</v>
       </c>
       <c r="C21">
         <v>5</v>
       </c>
       <c r="D21">
-        <v>1509.3</v>
+        <v>1318.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>08/02</v>
+        <v>08/09</v>
       </c>
       <c r="B22">
-        <v>302</v>
+        <v>238</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22">
-        <v>302</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>08/03</v>
+        <v>08/10</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>08/04</v>
+        <v>08/11</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -737,77 +737,77 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>08/05</v>
+        <v>08/12</v>
       </c>
       <c r="B25">
-        <v>271.49</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>271.49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>08/06</v>
+        <v>08/13</v>
       </c>
       <c r="B26">
-        <v>298.55</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>597.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>08/07</v>
+        <v>08/14</v>
       </c>
       <c r="B27">
-        <v>354.65</v>
+        <v>318.75</v>
       </c>
       <c r="C27">
         <v>4</v>
       </c>
       <c r="D27">
-        <v>1418.6</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>08/08</v>
+        <v>08/15</v>
       </c>
       <c r="B28">
-        <v>336.6333333333333</v>
+        <v>284.84000000000003</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D28">
-        <v>1009.9</v>
+        <v>1424.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>08/09</v>
+        <v>08/16</v>
       </c>
       <c r="B29">
-        <v>0</v>
+        <v>169.685</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>339.37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>08/10</v>
+        <v>08/17</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -821,7 +821,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>08/11</v>
+        <v>08/18</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -835,7 +835,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>08/12</v>
+        <v>08/19</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -849,7 +849,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>08/13</v>
+        <v>08/20</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -863,63 +863,63 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>08/14</v>
+        <v>08/21</v>
       </c>
       <c r="B34">
-        <v>328.5</v>
+        <v>287</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>657</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>08/15</v>
+        <v>08/22</v>
       </c>
       <c r="B35">
-        <v>280.73333333333335</v>
+        <v>290</v>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>842.2</v>
+        <v>290</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>08/16</v>
+        <v>08/23</v>
       </c>
       <c r="B36">
-        <v>167.4</v>
+        <v>197.1</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36">
-        <v>167.4</v>
+        <v>394.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>08/17</v>
+        <v>08/24</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>233.1</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>233.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>08/18</v>
+        <v>08/25</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -933,7 +933,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>08/19</v>
+        <v>08/26</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -947,7 +947,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>08/20</v>
+        <v>08/27</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -961,7 +961,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>08/21</v>
+        <v>08/28</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -975,7 +975,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>08/22</v>
+        <v>08/29</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -989,21 +989,21 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>08/23</v>
+        <v>08/30</v>
       </c>
       <c r="B43">
-        <v>161.1</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>161.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>08/24</v>
+        <v>08/31</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>08/25</v>
+        <v>09/01</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1031,217 +1031,217 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>08/26</v>
+        <v>09/02</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>215</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>08/27</v>
+        <v>09/03</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>226.5</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>453</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>08/28</v>
+        <v>09/04</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>460</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>08/29</v>
+        <v>09/05</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>388.5</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>777</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>08/30</v>
+        <v>09/06</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>388.5</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>777</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>08/31</v>
+        <v>09/07</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>209.9</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>419.8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>09/01</v>
+        <v>09/08</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>213.25</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>426.5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>09/02</v>
+        <v>09/09</v>
       </c>
       <c r="B53">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C53">
         <v>1</v>
       </c>
       <c r="D53">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>09/03</v>
+        <v>09/10</v>
       </c>
       <c r="B54">
-        <v>226.5</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>09/04</v>
+        <v>09/11</v>
       </c>
       <c r="B55">
-        <v>460</v>
+        <v>0</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>460</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>09/05</v>
+        <v>09/12</v>
       </c>
       <c r="B56">
-        <v>438</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>438</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>09/06</v>
+        <v>09/13</v>
       </c>
       <c r="B57">
-        <v>438</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>438</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>09/07</v>
+        <v>09/14</v>
       </c>
       <c r="B58">
-        <v>209.9</v>
+        <v>0</v>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>419.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>09/08</v>
+        <v>09/15</v>
       </c>
       <c r="B59">
-        <v>213.25</v>
+        <v>0</v>
       </c>
       <c r="C59">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>426.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>09/09</v>
+        <v>09/16</v>
       </c>
       <c r="B60">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>09/10</v>
+        <v>09/17</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>09/11</v>
+        <v>09/18</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -1269,7 +1269,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>09/12</v>
+        <v>09/19</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -1283,7 +1283,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>09/13</v>
+        <v>09/20</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>09/14</v>
+        <v>09/21</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>09/15</v>
+        <v>09/22</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>09/16</v>
+        <v>09/23</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1339,7 +1339,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>09/17</v>
+        <v>09/24</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1353,35 +1353,35 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>09/18</v>
+        <v>09/25</v>
       </c>
       <c r="B69">
-        <v>0</v>
+        <v>262.5</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>09/19</v>
+        <v>09/26</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>262.5</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>09/20</v>
+        <v>09/27</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>09/21</v>
+        <v>09/28</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>09/22</v>
+        <v>09/29</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>09/23</v>
+        <v>09/30</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>09/24</v>
+        <v>10/01</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1451,63 +1451,63 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>09/25</v>
+        <v>10/02</v>
       </c>
       <c r="B76">
-        <v>262.5</v>
+        <v>0</v>
       </c>
       <c r="C76">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>1050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>09/26</v>
+        <v>10/03</v>
       </c>
       <c r="B77">
-        <v>262.5</v>
+        <v>0</v>
       </c>
       <c r="C77">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>1050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>09/27</v>
+        <v>10/04</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>09/28</v>
+        <v>10/05</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>165</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>09/29</v>
+        <v>10/06</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>09/30</v>
+        <v>10/07</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>10/01</v>
+        <v>10/08</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>10/02</v>
+        <v>10/09</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>10/03</v>
+        <v>10/10</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1577,7 +1577,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>10/04</v>
+        <v>10/11</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>10/05</v>
+        <v>10/12</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>10/06</v>
+        <v>10/13</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>10/07</v>
+        <v>10/14</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1633,63 +1633,63 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>10/08</v>
+        <v>10/15</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>10/09</v>
+        <v>10/16</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>443</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>443</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>10/10</v>
+        <v>10/17</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>394</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>10/11</v>
+        <v>10/18</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>278</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>10/12</v>
+        <v>10/19</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>10/13</v>
+        <v>10/20</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>10/14</v>
+        <v>10/21</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1731,35 +1731,35 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>10/15</v>
+        <v>10/22</v>
       </c>
       <c r="B96">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96">
-        <v>356</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>10/16</v>
+        <v>10/23</v>
       </c>
       <c r="B97">
-        <v>443</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>10/17</v>
+        <v>10/24</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>10/18</v>
+        <v>10/25</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>10/19</v>
+        <v>10/26</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>10/20</v>
+        <v>10/27</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>10/21</v>
+        <v>10/28</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,7 +1829,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>10/22</v>
+        <v>10/29</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>10/23</v>
+        <v>10/30</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>10/24</v>
+        <v>10/31</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1871,7 +1871,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>10/25</v>
+        <v>11/01</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>10/26</v>
+        <v>11/02</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>10/27</v>
+        <v>11/03</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>10/28</v>
+        <v>11/04</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>10/29</v>
+        <v>11/05</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>10/30</v>
+        <v>11/06</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>10/31</v>
+        <v>11/07</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1969,21 +1969,21 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>11/01</v>
+        <v>11/08</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>188.1</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>188.1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>11/02</v>
+        <v>11/09</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>11/03</v>
+        <v>11/10</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>11/04</v>
+        <v>11/11</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>11/05</v>
+        <v>11/12</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>11/06</v>
+        <v>11/13</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>11/07</v>
+        <v>11/14</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>11/08</v>
+        <v>11/15</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>11/09</v>
+        <v>11/16</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>11/10</v>
+        <v>11/17</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>11/11</v>
+        <v>11/18</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -2123,49 +2123,49 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>11/12</v>
+        <v>11/19</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>11/13</v>
+        <v>11/20</v>
       </c>
       <c r="B125">
-        <v>367</v>
+        <v>288</v>
       </c>
       <c r="C125">
         <v>1</v>
       </c>
       <c r="D125">
-        <v>367</v>
+        <v>288</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>11/14</v>
+        <v>11/21</v>
       </c>
       <c r="B126">
-        <v>382</v>
+        <v>299</v>
       </c>
       <c r="C126">
         <v>1</v>
       </c>
       <c r="D126">
-        <v>382</v>
+        <v>299</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>11/15</v>
+        <v>11/22</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>11/16</v>
+        <v>11/23</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>11/17</v>
+        <v>11/24</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -2207,7 +2207,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>11/18</v>
+        <v>11/25</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>11/19</v>
+        <v>11/26</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>11/20</v>
+        <v>11/27</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>11/21</v>
+        <v>11/28</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -2263,7 +2263,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>11/22</v>
+        <v>11/29</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>11/23</v>
+        <v>11/30</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -2291,7 +2291,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>11/24</v>
+        <v>12/01</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>11/25</v>
+        <v>12/02</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>11/26</v>
+        <v>12/03</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>11/27</v>
+        <v>12/04</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>11/28</v>
+        <v>12/05</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>11/29</v>
+        <v>12/06</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -2375,7 +2375,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>11/30</v>
+        <v>12/07</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -2389,7 +2389,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>12/01</v>
+        <v>12/08</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -2403,7 +2403,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>12/02</v>
+        <v>12/09</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>12/03</v>
+        <v>12/10</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>12/04</v>
+        <v>12/11</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>12/05</v>
+        <v>12/12</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -2459,7 +2459,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>12/06</v>
+        <v>12/13</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -2473,7 +2473,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>12/07</v>
+        <v>12/14</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>12/08</v>
+        <v>12/15</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -2501,7 +2501,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>12/09</v>
+        <v>12/16</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -2515,7 +2515,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>12/10</v>
+        <v>12/17</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>12/11</v>
+        <v>12/18</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>12/12</v>
+        <v>12/19</v>
       </c>
       <c r="B154">
         <v>0</v>

--- a/ok-fc_occupancy_pace_150day.xlsx
+++ b/ok-fc_occupancy_pace_150day.xlsx
@@ -415,315 +415,315 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>07/20</v>
+        <v>07/27</v>
       </c>
       <c r="B2">
-        <v>166.62666666666667</v>
+        <v>198.87142857142857</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D2">
-        <v>499.88</v>
+        <v>1392.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>07/21</v>
+        <v>07/28</v>
       </c>
       <c r="B3">
-        <v>182.42999999999998</v>
+        <v>197.5111111111111</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>547.29</v>
+        <v>1777.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>07/22</v>
+        <v>07/29</v>
       </c>
       <c r="B4">
-        <v>191.25</v>
+        <v>231.62857142857143</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D4">
-        <v>573.75</v>
+        <v>1621.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>07/23</v>
+        <v>07/30</v>
       </c>
       <c r="B5">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>526</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>07/24</v>
+        <v>07/31</v>
       </c>
       <c r="B6">
-        <v>294.6644444444444</v>
+        <v>282.4909090909091</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>2651.98</v>
+        <v>3107.4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>07/25</v>
+        <v>08/01</v>
       </c>
       <c r="B7">
-        <v>276.47555555555556</v>
+        <v>271.6625</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>2488.28</v>
+        <v>2173.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>07/26</v>
+        <v>08/02</v>
       </c>
       <c r="B8">
-        <v>242.4857142857143</v>
+        <v>204.25</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8">
-        <v>1697.4</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>07/27</v>
+        <v>08/03</v>
       </c>
       <c r="B9">
-        <v>193.42000000000002</v>
+        <v>227.16666666666666</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>967.1</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>07/28</v>
+        <v>08/04</v>
       </c>
       <c r="B10">
-        <v>196.94285714285715</v>
+        <v>244</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>1378.6000000000001</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>07/29</v>
+        <v>08/05</v>
       </c>
       <c r="B11">
-        <v>239.08</v>
+        <v>253.16333333333333</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>1195.4</v>
+        <v>759.49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>07/30</v>
+        <v>08/06</v>
       </c>
       <c r="B12">
-        <v>269</v>
+        <v>285.525</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12">
-        <v>1345</v>
+        <v>1142.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>07/31</v>
+        <v>08/07</v>
       </c>
       <c r="B13">
-        <v>296.6</v>
+        <v>303.06666666666666</v>
       </c>
       <c r="C13">
         <v>9</v>
       </c>
       <c r="D13">
-        <v>2669.4</v>
+        <v>2727.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>08/01</v>
+        <v>08/08</v>
       </c>
       <c r="B14">
-        <v>290.21666666666664</v>
+        <v>254.10000000000002</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D14">
-        <v>1741.3</v>
+        <v>2286.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>08/02</v>
+        <v>08/09</v>
       </c>
       <c r="B15">
-        <v>259.2</v>
+        <v>238</v>
       </c>
       <c r="C15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>1296</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>08/03</v>
+        <v>08/10</v>
       </c>
       <c r="B16">
-        <v>236.8</v>
+        <v>229</v>
       </c>
       <c r="C16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>1184</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>08/04</v>
+        <v>08/11</v>
       </c>
       <c r="B17">
-        <v>259</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>08/05</v>
+        <v>08/12</v>
       </c>
       <c r="B18">
-        <v>265.245</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>530.49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>08/06</v>
+        <v>08/13</v>
       </c>
       <c r="B19">
-        <v>294.3666666666667</v>
+        <v>187</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>883.1</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>08/07</v>
+        <v>08/14</v>
       </c>
       <c r="B20">
-        <v>352.71999999999997</v>
+        <v>270.07142857142856</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D20">
-        <v>1763.6</v>
+        <v>1890.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>08/08</v>
+        <v>08/15</v>
       </c>
       <c r="B21">
-        <v>263.78000000000003</v>
+        <v>259.75714285714287</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D21">
-        <v>1318.9</v>
+        <v>1818.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>08/09</v>
+        <v>08/16</v>
       </c>
       <c r="B22">
-        <v>238</v>
+        <v>169.685</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22">
-        <v>238</v>
+        <v>339.37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>08/10</v>
+        <v>08/17</v>
       </c>
       <c r="B23">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>08/11</v>
+        <v>08/18</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -737,7 +737,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>08/12</v>
+        <v>08/19</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -751,7 +751,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>08/13</v>
+        <v>08/20</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -765,63 +765,63 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>08/14</v>
+        <v>08/21</v>
       </c>
       <c r="B27">
-        <v>318.75</v>
+        <v>287</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>1275</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>08/15</v>
+        <v>08/22</v>
       </c>
       <c r="B28">
-        <v>284.84000000000003</v>
+        <v>290</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>1424.2</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>08/16</v>
+        <v>08/23</v>
       </c>
       <c r="B29">
-        <v>169.685</v>
+        <v>197.1</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
       <c r="D29">
-        <v>339.37</v>
+        <v>394.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>08/17</v>
+        <v>08/24</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>233.1</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>233.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>08/18</v>
+        <v>08/25</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -835,7 +835,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>08/19</v>
+        <v>08/26</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -849,7 +849,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>08/20</v>
+        <v>08/27</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -863,63 +863,63 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>08/21</v>
+        <v>08/28</v>
       </c>
       <c r="B34">
-        <v>287</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>287</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>08/22</v>
+        <v>08/29</v>
       </c>
       <c r="B35">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>290</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>08/23</v>
+        <v>08/30</v>
       </c>
       <c r="B36">
-        <v>197.1</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>394.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>08/24</v>
+        <v>08/31</v>
       </c>
       <c r="B37">
-        <v>233.1</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>233.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>08/25</v>
+        <v>09/01</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -933,217 +933,217 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>08/26</v>
+        <v>09/02</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>08/27</v>
+        <v>09/03</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>226.5</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>453</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>08/28</v>
+        <v>09/04</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>460</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>460</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>08/29</v>
+        <v>09/05</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>388.5</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>777</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>08/30</v>
+        <v>09/06</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>388.5</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>777</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>08/31</v>
+        <v>09/07</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>209.9</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>419.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>09/01</v>
+        <v>09/08</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>213.25</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>426.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>09/02</v>
+        <v>09/09</v>
       </c>
       <c r="B46">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C46">
         <v>1</v>
       </c>
       <c r="D46">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>09/03</v>
+        <v>09/10</v>
       </c>
       <c r="B47">
-        <v>226.5</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>09/04</v>
+        <v>09/11</v>
       </c>
       <c r="B48">
-        <v>460</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>460</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>09/05</v>
+        <v>09/12</v>
       </c>
       <c r="B49">
-        <v>388.5</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>09/06</v>
+        <v>09/13</v>
       </c>
       <c r="B50">
-        <v>388.5</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>09/07</v>
+        <v>09/14</v>
       </c>
       <c r="B51">
-        <v>209.9</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>419.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>09/08</v>
+        <v>09/15</v>
       </c>
       <c r="B52">
-        <v>213.25</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>426.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>09/09</v>
+        <v>09/16</v>
       </c>
       <c r="B53">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>09/10</v>
+        <v>09/17</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>09/11</v>
+        <v>09/18</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -1171,7 +1171,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>09/12</v>
+        <v>09/19</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>09/13</v>
+        <v>09/20</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1199,49 +1199,49 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>09/14</v>
+        <v>09/21</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>261</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>09/15</v>
+        <v>09/22</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>259</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>09/16</v>
+        <v>09/23</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>256</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>09/17</v>
+        <v>09/24</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1255,35 +1255,35 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>09/18</v>
+        <v>09/25</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>262.5</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>09/19</v>
+        <v>09/26</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>262.5</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>09/20</v>
+        <v>09/27</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>09/21</v>
+        <v>09/28</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>09/22</v>
+        <v>09/29</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>09/23</v>
+        <v>09/30</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1339,7 +1339,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>09/24</v>
+        <v>10/01</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -1353,63 +1353,63 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>09/25</v>
+        <v>10/02</v>
       </c>
       <c r="B69">
-        <v>262.5</v>
+        <v>237.67</v>
       </c>
       <c r="C69">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D69">
-        <v>1050</v>
+        <v>237.67</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>09/26</v>
+        <v>10/03</v>
       </c>
       <c r="B70">
-        <v>262.5</v>
+        <v>226.08</v>
       </c>
       <c r="C70">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D70">
-        <v>1050</v>
+        <v>226.08</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>09/27</v>
+        <v>10/04</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>09/28</v>
+        <v>10/05</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>165</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>09/29</v>
+        <v>10/06</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>09/30</v>
+        <v>10/07</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1437,77 +1437,77 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>10/01</v>
+        <v>10/08</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>302</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>10/02</v>
+        <v>10/09</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>10/03</v>
+        <v>10/10</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>356</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>10/04</v>
+        <v>10/11</v>
       </c>
       <c r="B78">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>10/05</v>
+        <v>10/12</v>
       </c>
       <c r="B79">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>10/06</v>
+        <v>10/13</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>10/07</v>
+        <v>10/14</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1535,63 +1535,63 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>10/08</v>
+        <v>10/15</v>
       </c>
       <c r="B82">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>356</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>10/09</v>
+        <v>10/16</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>393.5</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>787</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>10/10</v>
+        <v>10/17</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>366.5</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>733</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>10/11</v>
+        <v>10/18</v>
       </c>
       <c r="B85">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>278</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>10/12</v>
+        <v>10/19</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>10/13</v>
+        <v>10/20</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>10/14</v>
+        <v>10/21</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1633,63 +1633,63 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>10/15</v>
+        <v>10/22</v>
       </c>
       <c r="B89">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>356</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>10/16</v>
+        <v>10/23</v>
       </c>
       <c r="B90">
-        <v>443</v>
+        <v>0</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>10/17</v>
+        <v>10/24</v>
       </c>
       <c r="B91">
-        <v>394</v>
+        <v>0</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>394</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>10/18</v>
+        <v>10/25</v>
       </c>
       <c r="B92">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>10/19</v>
+        <v>10/26</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>10/20</v>
+        <v>10/27</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>10/21</v>
+        <v>10/28</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>10/22</v>
+        <v>10/29</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>10/23</v>
+        <v>10/30</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>10/24</v>
+        <v>10/31</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1773,7 +1773,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>10/25</v>
+        <v>11/01</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>10/26</v>
+        <v>11/02</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>10/27</v>
+        <v>11/03</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>10/28</v>
+        <v>11/04</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,7 +1829,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>10/29</v>
+        <v>11/05</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>10/30</v>
+        <v>11/06</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>10/31</v>
+        <v>11/07</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1871,21 +1871,21 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>11/01</v>
+        <v>11/08</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>188.1</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>188.1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>11/02</v>
+        <v>11/09</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>11/03</v>
+        <v>11/10</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>11/04</v>
+        <v>11/11</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>11/05</v>
+        <v>11/12</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>11/06</v>
+        <v>11/13</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>11/07</v>
+        <v>11/14</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1969,21 +1969,21 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>11/08</v>
+        <v>11/15</v>
       </c>
       <c r="B113">
-        <v>188.1</v>
+        <v>0</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>188.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>11/09</v>
+        <v>11/16</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>11/10</v>
+        <v>11/17</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>11/11</v>
+        <v>11/18</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2025,49 +2025,49 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>11/12</v>
+        <v>11/19</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>11/13</v>
+        <v>11/20</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>288</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>11/14</v>
+        <v>11/21</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>299</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>11/15</v>
+        <v>11/22</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>11/16</v>
+        <v>11/23</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>11/17</v>
+        <v>11/24</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>11/18</v>
+        <v>11/25</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -2123,49 +2123,49 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>11/19</v>
+        <v>11/26</v>
       </c>
       <c r="B124">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="C124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D124">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>11/20</v>
+        <v>11/27</v>
       </c>
       <c r="B125">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="C125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D125">
-        <v>288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>11/21</v>
+        <v>11/28</v>
       </c>
       <c r="B126">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="C126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D126">
-        <v>299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>11/22</v>
+        <v>11/29</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>11/23</v>
+        <v>11/30</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>11/24</v>
+        <v>12/01</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -2207,7 +2207,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>11/25</v>
+        <v>12/02</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>11/26</v>
+        <v>12/03</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -2235,7 +2235,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>11/27</v>
+        <v>12/04</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -2249,7 +2249,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>11/28</v>
+        <v>12/05</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -2263,7 +2263,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>11/29</v>
+        <v>12/06</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>11/30</v>
+        <v>12/07</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -2291,7 +2291,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>12/01</v>
+        <v>12/08</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>12/02</v>
+        <v>12/09</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>12/03</v>
+        <v>12/10</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>12/04</v>
+        <v>12/11</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>12/05</v>
+        <v>12/12</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>12/06</v>
+        <v>12/13</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -2375,7 +2375,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>12/07</v>
+        <v>12/14</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -2389,7 +2389,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>12/08</v>
+        <v>12/15</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -2403,7 +2403,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>12/09</v>
+        <v>12/16</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -2417,7 +2417,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>12/10</v>
+        <v>12/17</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>12/11</v>
+        <v>12/18</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -2445,7 +2445,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>12/12</v>
+        <v>12/19</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -2459,7 +2459,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>12/13</v>
+        <v>12/20</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -2473,7 +2473,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>12/14</v>
+        <v>12/21</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>12/15</v>
+        <v>12/22</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -2501,7 +2501,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>12/16</v>
+        <v>12/23</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -2515,7 +2515,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>12/17</v>
+        <v>12/24</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -2529,7 +2529,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>12/18</v>
+        <v>12/25</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>12/19</v>
+        <v>12/26</v>
       </c>
       <c r="B154">
         <v>0</v>

--- a/ok-fc_occupancy_pace_150day.xlsx
+++ b/ok-fc_occupancy_pace_150day.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D154"/>
+  <dimension ref="A1:D124"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,217 +415,217 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>07/27</v>
+        <v>08/03</v>
       </c>
       <c r="B2">
-        <v>198.87142857142857</v>
+        <v>232.16666666666666</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>1392.1</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>07/28</v>
+        <v>08/04</v>
       </c>
       <c r="B3">
-        <v>197.5111111111111</v>
+        <v>219</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>1777.6</v>
+        <v>876</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>07/29</v>
+        <v>08/05</v>
       </c>
       <c r="B4">
-        <v>231.62857142857143</v>
+        <v>253.16333333333333</v>
       </c>
       <c r="C4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>1621.4</v>
+        <v>759.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>07/30</v>
+        <v>08/06</v>
       </c>
       <c r="B5">
-        <v>269</v>
+        <v>264.02</v>
       </c>
       <c r="C5">
         <v>5</v>
       </c>
       <c r="D5">
-        <v>1345</v>
+        <v>1320.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>07/31</v>
+        <v>08/07</v>
       </c>
       <c r="B6">
-        <v>282.4909090909091</v>
+        <v>295.84444444444443</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>3107.4</v>
+        <v>2662.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>08/01</v>
+        <v>08/08</v>
       </c>
       <c r="B7">
-        <v>271.6625</v>
+        <v>253.69</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>2173.3</v>
+        <v>2536.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>08/02</v>
+        <v>08/09</v>
       </c>
       <c r="B8">
-        <v>204.25</v>
+        <v>246.75</v>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D8">
-        <v>1634</v>
+        <v>987</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>08/03</v>
+        <v>08/10</v>
       </c>
       <c r="B9">
-        <v>227.16666666666666</v>
+        <v>236.66666666666666</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>1363</v>
+        <v>710</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>08/04</v>
+        <v>08/11</v>
       </c>
       <c r="B10">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>08/05</v>
+        <v>08/12</v>
       </c>
       <c r="B11">
-        <v>253.16333333333333</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>759.49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>08/06</v>
+        <v>08/13</v>
       </c>
       <c r="B12">
-        <v>285.525</v>
+        <v>187</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>1142.1</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>08/07</v>
+        <v>08/14</v>
       </c>
       <c r="B13">
-        <v>303.06666666666666</v>
+        <v>258.05555555555554</v>
       </c>
       <c r="C13">
         <v>9</v>
       </c>
       <c r="D13">
-        <v>2727.6</v>
+        <v>2322.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>08/08</v>
+        <v>08/15</v>
       </c>
       <c r="B14">
-        <v>254.10000000000002</v>
+        <v>247.2555555555556</v>
       </c>
       <c r="C14">
         <v>9</v>
       </c>
       <c r="D14">
-        <v>2286.9</v>
+        <v>2225.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>08/09</v>
+        <v>08/16</v>
       </c>
       <c r="B15">
-        <v>238</v>
+        <v>169.685</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>238</v>
+        <v>339.37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>08/10</v>
+        <v>08/17</v>
       </c>
       <c r="B16">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>08/11</v>
+        <v>08/18</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -639,7 +639,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>08/12</v>
+        <v>08/19</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -653,77 +653,77 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>08/13</v>
+        <v>08/20</v>
       </c>
       <c r="B19">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>08/14</v>
+        <v>08/21</v>
       </c>
       <c r="B20">
-        <v>270.07142857142856</v>
+        <v>253.85</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D20">
-        <v>1890.5</v>
+        <v>1015.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>08/15</v>
+        <v>08/22</v>
       </c>
       <c r="B21">
-        <v>259.75714285714287</v>
+        <v>257.4</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D21">
-        <v>1818.3</v>
+        <v>1029.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>08/16</v>
+        <v>08/23</v>
       </c>
       <c r="B22">
-        <v>169.685</v>
+        <v>197.1</v>
       </c>
       <c r="C22">
         <v>2</v>
       </c>
       <c r="D22">
-        <v>339.37</v>
+        <v>394.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>08/17</v>
+        <v>08/24</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>196.05</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>392.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>08/18</v>
+        <v>08/25</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -737,7 +737,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>08/19</v>
+        <v>08/26</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -751,7 +751,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>08/20</v>
+        <v>08/27</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -765,63 +765,63 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>08/21</v>
+        <v>08/28</v>
       </c>
       <c r="B27">
-        <v>287</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>287</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>08/22</v>
+        <v>08/29</v>
       </c>
       <c r="B28">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28">
-        <v>290</v>
+        <v>312</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>08/23</v>
+        <v>08/30</v>
       </c>
       <c r="B29">
-        <v>197.1</v>
+        <v>241</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>394.2</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>08/24</v>
+        <v>08/31</v>
       </c>
       <c r="B30">
-        <v>233.1</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>233.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>08/25</v>
+        <v>09/01</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -835,217 +835,217 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>08/26</v>
+        <v>09/02</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>08/27</v>
+        <v>09/03</v>
       </c>
       <c r="B33">
-        <v>0</v>
+        <v>226.5</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>453</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>08/28</v>
+        <v>09/04</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>356.25</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>08/29</v>
+        <v>09/05</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>348.6</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>08/30</v>
+        <v>09/06</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>388.5</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>777</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>08/31</v>
+        <v>09/07</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>209.9</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>419.8</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>09/01</v>
+        <v>09/08</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>213.25</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>426.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>09/02</v>
+        <v>09/09</v>
       </c>
       <c r="B39">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>09/03</v>
+        <v>09/10</v>
       </c>
       <c r="B40">
-        <v>226.5</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>09/04</v>
+        <v>09/11</v>
       </c>
       <c r="B41">
-        <v>460</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>460</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>09/05</v>
+        <v>09/12</v>
       </c>
       <c r="B42">
-        <v>388.5</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>09/06</v>
+        <v>09/13</v>
       </c>
       <c r="B43">
-        <v>388.5</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>09/07</v>
+        <v>09/14</v>
       </c>
       <c r="B44">
-        <v>209.9</v>
+        <v>160</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D44">
-        <v>419.8</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>09/08</v>
+        <v>09/15</v>
       </c>
       <c r="B45">
-        <v>213.25</v>
+        <v>159</v>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45">
-        <v>426.5</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>09/09</v>
+        <v>09/16</v>
       </c>
       <c r="B46">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>09/10</v>
+        <v>09/17</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>09/11</v>
+        <v>09/18</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>09/12</v>
+        <v>09/19</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>09/13</v>
+        <v>09/20</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1101,49 +1101,49 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>09/14</v>
+        <v>09/21</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>261</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>09/15</v>
+        <v>09/22</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>259</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>259</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>09/16</v>
+        <v>09/23</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>256</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>09/17</v>
+        <v>09/24</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1157,35 +1157,35 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>09/18</v>
+        <v>09/25</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>262.5</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>09/19</v>
+        <v>09/26</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>262.5</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>09/20</v>
+        <v>09/27</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -1199,49 +1199,49 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>09/21</v>
+        <v>09/28</v>
       </c>
       <c r="B58">
-        <v>261</v>
+        <v>0</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>09/22</v>
+        <v>09/29</v>
       </c>
       <c r="B59">
-        <v>259</v>
+        <v>0</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>09/23</v>
+        <v>09/30</v>
       </c>
       <c r="B60">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>09/24</v>
+        <v>10/01</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -1255,63 +1255,63 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>09/25</v>
+        <v>10/02</v>
       </c>
       <c r="B62">
-        <v>262.5</v>
+        <v>237.67</v>
       </c>
       <c r="C62">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D62">
-        <v>1050</v>
+        <v>237.67</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>09/26</v>
+        <v>10/03</v>
       </c>
       <c r="B63">
-        <v>262.5</v>
+        <v>226.08</v>
       </c>
       <c r="C63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>1050</v>
+        <v>226.08</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>09/27</v>
+        <v>10/04</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>09/28</v>
+        <v>10/05</v>
       </c>
       <c r="B65">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>165</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>09/29</v>
+        <v>10/06</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>09/30</v>
+        <v>10/07</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1339,77 +1339,77 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>10/01</v>
+        <v>10/08</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>302</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>10/02</v>
+        <v>10/09</v>
       </c>
       <c r="B69">
-        <v>237.67</v>
+        <v>292</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69">
-        <v>237.67</v>
+        <v>584</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>10/03</v>
+        <v>10/10</v>
       </c>
       <c r="B70">
-        <v>226.08</v>
+        <v>291</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70">
-        <v>226.08</v>
+        <v>582</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>10/04</v>
+        <v>10/11</v>
       </c>
       <c r="B71">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>10/05</v>
+        <v>10/12</v>
       </c>
       <c r="B72">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>10/06</v>
+        <v>10/13</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>10/07</v>
+        <v>10/14</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1437,63 +1437,63 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>10/08</v>
+        <v>10/15</v>
       </c>
       <c r="B75">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="C75">
         <v>1</v>
       </c>
       <c r="D75">
-        <v>302</v>
+        <v>356</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>10/09</v>
+        <v>10/16</v>
       </c>
       <c r="B76">
-        <v>360</v>
+        <v>393.5</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D76">
-        <v>360</v>
+        <v>787</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>10/10</v>
+        <v>10/17</v>
       </c>
       <c r="B77">
-        <v>356</v>
+        <v>366.5</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D77">
-        <v>356</v>
+        <v>733</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>10/11</v>
+        <v>10/18</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>278</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>10/12</v>
+        <v>10/19</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1507,7 +1507,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>10/13</v>
+        <v>10/20</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>10/14</v>
+        <v>10/21</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1535,63 +1535,63 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>10/15</v>
+        <v>10/22</v>
       </c>
       <c r="B82">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>356</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>10/16</v>
+        <v>10/23</v>
       </c>
       <c r="B83">
-        <v>393.5</v>
+        <v>0</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>787</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>10/17</v>
+        <v>10/24</v>
       </c>
       <c r="B84">
-        <v>366.5</v>
+        <v>0</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D84">
-        <v>733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>10/18</v>
+        <v>10/25</v>
       </c>
       <c r="B85">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>10/19</v>
+        <v>10/26</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>10/20</v>
+        <v>10/27</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>10/21</v>
+        <v>10/28</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>10/22</v>
+        <v>10/29</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1647,7 +1647,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>10/23</v>
+        <v>10/30</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1661,7 +1661,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>10/24</v>
+        <v>10/31</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>10/25</v>
+        <v>11/01</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>10/26</v>
+        <v>11/02</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>10/27</v>
+        <v>11/03</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>10/28</v>
+        <v>11/04</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>10/29</v>
+        <v>11/05</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>10/30</v>
+        <v>11/06</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>10/31</v>
+        <v>11/07</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1773,21 +1773,21 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>11/01</v>
+        <v>11/08</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>188.1</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>188.1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>11/02</v>
+        <v>11/09</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>11/03</v>
+        <v>11/10</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>11/04</v>
+        <v>11/11</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,7 +1829,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>11/05</v>
+        <v>11/12</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>11/06</v>
+        <v>11/13</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>11/07</v>
+        <v>11/14</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1871,21 +1871,21 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>11/08</v>
+        <v>11/15</v>
       </c>
       <c r="B106">
-        <v>188.1</v>
+        <v>0</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D106">
-        <v>188.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>11/09</v>
+        <v>11/16</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>11/10</v>
+        <v>11/17</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>11/11</v>
+        <v>11/18</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1927,49 +1927,49 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>11/12</v>
+        <v>11/19</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>11/13</v>
+        <v>11/20</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>288</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>11/14</v>
+        <v>11/21</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>299</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>11/15</v>
+        <v>11/22</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>11/16</v>
+        <v>11/23</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>11/17</v>
+        <v>11/24</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>11/18</v>
+        <v>11/25</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2025,49 +2025,49 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>11/19</v>
+        <v>11/26</v>
       </c>
       <c r="B117">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>11/20</v>
+        <v>11/27</v>
       </c>
       <c r="B118">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="C118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>11/21</v>
+        <v>11/28</v>
       </c>
       <c r="B119">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="C119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>11/22</v>
+        <v>11/29</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>11/23</v>
+        <v>11/30</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>11/24</v>
+        <v>12/01</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>11/25</v>
+        <v>12/02</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>11/26</v>
+        <v>12/03</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -2132,432 +2132,12 @@
         <v>0</v>
       </c>
       <c r="D124">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v>11/27</v>
-      </c>
-      <c r="B125">
-        <v>0</v>
-      </c>
-      <c r="C125">
-        <v>0</v>
-      </c>
-      <c r="D125">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v>11/28</v>
-      </c>
-      <c r="B126">
-        <v>0</v>
-      </c>
-      <c r="C126">
-        <v>0</v>
-      </c>
-      <c r="D126">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v>11/29</v>
-      </c>
-      <c r="B127">
-        <v>0</v>
-      </c>
-      <c r="C127">
-        <v>0</v>
-      </c>
-      <c r="D127">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v>11/30</v>
-      </c>
-      <c r="B128">
-        <v>0</v>
-      </c>
-      <c r="C128">
-        <v>0</v>
-      </c>
-      <c r="D128">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>12/01</v>
-      </c>
-      <c r="B129">
-        <v>0</v>
-      </c>
-      <c r="C129">
-        <v>0</v>
-      </c>
-      <c r="D129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v>12/02</v>
-      </c>
-      <c r="B130">
-        <v>0</v>
-      </c>
-      <c r="C130">
-        <v>0</v>
-      </c>
-      <c r="D130">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="str">
-        <v>12/03</v>
-      </c>
-      <c r="B131">
-        <v>0</v>
-      </c>
-      <c r="C131">
-        <v>0</v>
-      </c>
-      <c r="D131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="str">
-        <v>12/04</v>
-      </c>
-      <c r="B132">
-        <v>0</v>
-      </c>
-      <c r="C132">
-        <v>0</v>
-      </c>
-      <c r="D132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>12/05</v>
-      </c>
-      <c r="B133">
-        <v>0</v>
-      </c>
-      <c r="C133">
-        <v>0</v>
-      </c>
-      <c r="D133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="str">
-        <v>12/06</v>
-      </c>
-      <c r="B134">
-        <v>0</v>
-      </c>
-      <c r="C134">
-        <v>0</v>
-      </c>
-      <c r="D134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v>12/07</v>
-      </c>
-      <c r="B135">
-        <v>0</v>
-      </c>
-      <c r="C135">
-        <v>0</v>
-      </c>
-      <c r="D135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="str">
-        <v>12/08</v>
-      </c>
-      <c r="B136">
-        <v>0</v>
-      </c>
-      <c r="C136">
-        <v>0</v>
-      </c>
-      <c r="D136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v>12/09</v>
-      </c>
-      <c r="B137">
-        <v>0</v>
-      </c>
-      <c r="C137">
-        <v>0</v>
-      </c>
-      <c r="D137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>12/10</v>
-      </c>
-      <c r="B138">
-        <v>0</v>
-      </c>
-      <c r="C138">
-        <v>0</v>
-      </c>
-      <c r="D138">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v>12/11</v>
-      </c>
-      <c r="B139">
-        <v>0</v>
-      </c>
-      <c r="C139">
-        <v>0</v>
-      </c>
-      <c r="D139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="str">
-        <v>12/12</v>
-      </c>
-      <c r="B140">
-        <v>0</v>
-      </c>
-      <c r="C140">
-        <v>0</v>
-      </c>
-      <c r="D140">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="str">
-        <v>12/13</v>
-      </c>
-      <c r="B141">
-        <v>0</v>
-      </c>
-      <c r="C141">
-        <v>0</v>
-      </c>
-      <c r="D141">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="str">
-        <v>12/14</v>
-      </c>
-      <c r="B142">
-        <v>0</v>
-      </c>
-      <c r="C142">
-        <v>0</v>
-      </c>
-      <c r="D142">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="str">
-        <v>12/15</v>
-      </c>
-      <c r="B143">
-        <v>0</v>
-      </c>
-      <c r="C143">
-        <v>0</v>
-      </c>
-      <c r="D143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="str">
-        <v>12/16</v>
-      </c>
-      <c r="B144">
-        <v>0</v>
-      </c>
-      <c r="C144">
-        <v>0</v>
-      </c>
-      <c r="D144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v>12/17</v>
-      </c>
-      <c r="B145">
-        <v>0</v>
-      </c>
-      <c r="C145">
-        <v>0</v>
-      </c>
-      <c r="D145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="str">
-        <v>12/18</v>
-      </c>
-      <c r="B146">
-        <v>0</v>
-      </c>
-      <c r="C146">
-        <v>0</v>
-      </c>
-      <c r="D146">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="str">
-        <v>12/19</v>
-      </c>
-      <c r="B147">
-        <v>0</v>
-      </c>
-      <c r="C147">
-        <v>0</v>
-      </c>
-      <c r="D147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="str">
-        <v>12/20</v>
-      </c>
-      <c r="B148">
-        <v>0</v>
-      </c>
-      <c r="C148">
-        <v>0</v>
-      </c>
-      <c r="D148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="str">
-        <v>12/21</v>
-      </c>
-      <c r="B149">
-        <v>0</v>
-      </c>
-      <c r="C149">
-        <v>0</v>
-      </c>
-      <c r="D149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="str">
-        <v>12/22</v>
-      </c>
-      <c r="B150">
-        <v>0</v>
-      </c>
-      <c r="C150">
-        <v>0</v>
-      </c>
-      <c r="D150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
-        <v>12/23</v>
-      </c>
-      <c r="B151">
-        <v>0</v>
-      </c>
-      <c r="C151">
-        <v>0</v>
-      </c>
-      <c r="D151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="str">
-        <v>12/24</v>
-      </c>
-      <c r="B152">
-        <v>0</v>
-      </c>
-      <c r="C152">
-        <v>0</v>
-      </c>
-      <c r="D152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
-        <v>12/25</v>
-      </c>
-      <c r="B153">
-        <v>0</v>
-      </c>
-      <c r="C153">
-        <v>0</v>
-      </c>
-      <c r="D153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="str">
-        <v>12/26</v>
-      </c>
-      <c r="B154">
-        <v>0</v>
-      </c>
-      <c r="C154">
-        <v>0</v>
-      </c>
-      <c r="D154">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D154"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D124"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ok-fc_occupancy_pace_150day.xlsx
+++ b/ok-fc_occupancy_pace_150day.xlsx
@@ -415,119 +415,119 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>08/03</v>
+        <v>08/10</v>
       </c>
       <c r="B2">
-        <v>232.16666666666666</v>
+        <v>236.66666666666666</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>1393</v>
+        <v>710</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>08/04</v>
+        <v>08/11</v>
       </c>
       <c r="B3">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>876</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>08/05</v>
+        <v>08/12</v>
       </c>
       <c r="B4">
-        <v>253.16333333333333</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>759.49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>08/06</v>
+        <v>08/13</v>
       </c>
       <c r="B5">
-        <v>264.02</v>
+        <v>93.5</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>1320.1</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>08/07</v>
+        <v>08/14</v>
       </c>
       <c r="B6">
-        <v>295.84444444444443</v>
+        <v>290.59090909090907</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>2662.6</v>
+        <v>3196.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>08/08</v>
+        <v>08/15</v>
       </c>
       <c r="B7">
-        <v>253.69</v>
+        <v>278.3</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>2536.9</v>
+        <v>3061.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>08/09</v>
+        <v>08/16</v>
       </c>
       <c r="B8">
-        <v>246.75</v>
+        <v>199.45666666666668</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>987</v>
+        <v>598.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>08/10</v>
+        <v>08/17</v>
       </c>
       <c r="B9">
-        <v>236.66666666666666</v>
+        <v>270</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>710</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>08/11</v>
+        <v>08/18</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>08/12</v>
+        <v>08/19</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -555,77 +555,77 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>08/13</v>
+        <v>08/20</v>
       </c>
       <c r="B12">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>08/14</v>
+        <v>08/21</v>
       </c>
       <c r="B13">
-        <v>258.05555555555554</v>
+        <v>283.848</v>
       </c>
       <c r="C13">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D13">
-        <v>2322.5</v>
+        <v>1419.24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>08/15</v>
+        <v>08/22</v>
       </c>
       <c r="B14">
-        <v>247.2555555555556</v>
+        <v>290.168</v>
       </c>
       <c r="C14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D14">
-        <v>2225.3</v>
+        <v>1450.8400000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>08/16</v>
+        <v>08/23</v>
       </c>
       <c r="B15">
-        <v>169.685</v>
+        <v>197.1</v>
       </c>
       <c r="C15">
         <v>2</v>
       </c>
       <c r="D15">
-        <v>339.37</v>
+        <v>394.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>08/17</v>
+        <v>08/24</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>196.05</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>392.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>08/18</v>
+        <v>08/25</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -639,7 +639,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>08/19</v>
+        <v>08/26</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -653,77 +653,77 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>08/20</v>
+        <v>08/27</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>522</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>522</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>08/21</v>
+        <v>08/28</v>
       </c>
       <c r="B20">
-        <v>253.85</v>
+        <v>616</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>1015.4</v>
+        <v>616</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>08/22</v>
+        <v>08/29</v>
       </c>
       <c r="B21">
-        <v>257.4</v>
+        <v>325.5</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>1029.6</v>
+        <v>651</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>08/23</v>
+        <v>08/30</v>
       </c>
       <c r="B22">
-        <v>197.1</v>
+        <v>311.24</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22">
-        <v>394.2</v>
+        <v>933.72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>08/24</v>
+        <v>08/31</v>
       </c>
       <c r="B23">
-        <v>196.05</v>
+        <v>395.72</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>392.1</v>
+        <v>395.72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>08/25</v>
+        <v>09/01</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -737,217 +737,217 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>08/26</v>
+        <v>09/02</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>08/27</v>
+        <v>09/03</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>226.5</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>453</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>08/28</v>
+        <v>09/04</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>355.5</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>2844</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>08/29</v>
+        <v>09/05</v>
       </c>
       <c r="B28">
-        <v>312</v>
+        <v>364.5</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D28">
-        <v>312</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>08/30</v>
+        <v>09/06</v>
       </c>
       <c r="B29">
-        <v>241</v>
+        <v>442.75</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D29">
-        <v>241</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>08/31</v>
+        <v>09/07</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>209.9</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>419.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>09/01</v>
+        <v>09/08</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>213.25</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>426.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>09/02</v>
+        <v>09/09</v>
       </c>
       <c r="B32">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>09/03</v>
+        <v>09/10</v>
       </c>
       <c r="B33">
-        <v>226.5</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>453</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>09/04</v>
+        <v>09/11</v>
       </c>
       <c r="B34">
-        <v>356.25</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>1425</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>09/05</v>
+        <v>09/12</v>
       </c>
       <c r="B35">
-        <v>348.6</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>1743</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>09/06</v>
+        <v>09/13</v>
       </c>
       <c r="B36">
-        <v>388.5</v>
+        <v>229</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36">
-        <v>777</v>
+        <v>229</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>09/07</v>
+        <v>09/14</v>
       </c>
       <c r="B37">
-        <v>209.9</v>
+        <v>194.5</v>
       </c>
       <c r="C37">
         <v>2</v>
       </c>
       <c r="D37">
-        <v>419.8</v>
+        <v>389</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>09/08</v>
+        <v>09/15</v>
       </c>
       <c r="B38">
-        <v>213.25</v>
+        <v>194</v>
       </c>
       <c r="C38">
         <v>2</v>
       </c>
       <c r="D38">
-        <v>426.5</v>
+        <v>388</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>09/09</v>
+        <v>09/16</v>
       </c>
       <c r="B39">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>09/10</v>
+        <v>09/17</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -961,7 +961,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>09/11</v>
+        <v>09/18</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -975,7 +975,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>09/12</v>
+        <v>09/19</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -989,7 +989,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>09/13</v>
+        <v>09/20</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1003,49 +1003,49 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>09/14</v>
+        <v>09/21</v>
       </c>
       <c r="B44">
-        <v>160</v>
+        <v>261</v>
       </c>
       <c r="C44">
         <v>1</v>
       </c>
       <c r="D44">
-        <v>160</v>
+        <v>261</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>09/15</v>
+        <v>09/22</v>
       </c>
       <c r="B45">
-        <v>159</v>
+        <v>259</v>
       </c>
       <c r="C45">
         <v>1</v>
       </c>
       <c r="D45">
-        <v>159</v>
+        <v>259</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>09/16</v>
+        <v>09/23</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>09/17</v>
+        <v>09/24</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1059,35 +1059,35 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>09/18</v>
+        <v>09/25</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>09/19</v>
+        <v>09/26</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>09/20</v>
+        <v>09/27</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -1101,49 +1101,49 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>09/21</v>
+        <v>09/28</v>
       </c>
       <c r="B51">
-        <v>261</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>09/22</v>
+        <v>09/29</v>
       </c>
       <c r="B52">
-        <v>259</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>09/23</v>
+        <v>09/30</v>
       </c>
       <c r="B53">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>09/24</v>
+        <v>10/01</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -1157,63 +1157,63 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>09/25</v>
+        <v>10/02</v>
       </c>
       <c r="B55">
-        <v>262.5</v>
+        <v>299.835</v>
       </c>
       <c r="C55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D55">
-        <v>1050</v>
+        <v>599.67</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>09/26</v>
+        <v>10/03</v>
       </c>
       <c r="B56">
-        <v>262.5</v>
+        <v>287.04</v>
       </c>
       <c r="C56">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D56">
-        <v>1050</v>
+        <v>574.08</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>09/27</v>
+        <v>10/04</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>09/28</v>
+        <v>10/05</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>165</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>09/29</v>
+        <v>10/06</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1227,7 +1227,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>09/30</v>
+        <v>10/07</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1241,77 +1241,77 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>10/01</v>
+        <v>10/08</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>302</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>10/02</v>
+        <v>10/09</v>
       </c>
       <c r="B62">
-        <v>237.67</v>
+        <v>302.25</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D62">
-        <v>237.67</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>10/03</v>
+        <v>10/10</v>
       </c>
       <c r="B63">
-        <v>226.08</v>
+        <v>298.5</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D63">
-        <v>226.08</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>10/04</v>
+        <v>10/11</v>
       </c>
       <c r="B64">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>10/05</v>
+        <v>10/12</v>
       </c>
       <c r="B65">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>10/06</v>
+        <v>10/13</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>10/07</v>
+        <v>10/14</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1339,63 +1339,63 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>10/08</v>
+        <v>10/15</v>
       </c>
       <c r="B68">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="C68">
         <v>1</v>
       </c>
       <c r="D68">
-        <v>302</v>
+        <v>356</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>10/09</v>
+        <v>10/16</v>
       </c>
       <c r="B69">
-        <v>292</v>
+        <v>381.6666666666667</v>
       </c>
       <c r="C69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D69">
-        <v>584</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>10/10</v>
+        <v>10/17</v>
       </c>
       <c r="B70">
-        <v>291</v>
+        <v>363.6666666666667</v>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D70">
-        <v>582</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>10/11</v>
+        <v>10/18</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>278</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>10/12</v>
+        <v>10/19</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>10/13</v>
+        <v>10/20</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>10/14</v>
+        <v>10/21</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1437,63 +1437,63 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>10/15</v>
+        <v>10/22</v>
       </c>
       <c r="B75">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>356</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>10/16</v>
+        <v>10/23</v>
       </c>
       <c r="B76">
-        <v>393.5</v>
+        <v>0</v>
       </c>
       <c r="C76">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>787</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>10/17</v>
+        <v>10/24</v>
       </c>
       <c r="B77">
-        <v>366.5</v>
+        <v>0</v>
       </c>
       <c r="C77">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>733</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>10/18</v>
+        <v>10/25</v>
       </c>
       <c r="B78">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>10/19</v>
+        <v>10/26</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1507,7 +1507,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>10/20</v>
+        <v>10/27</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>10/21</v>
+        <v>10/28</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>10/22</v>
+        <v>10/29</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>10/23</v>
+        <v>10/30</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>10/24</v>
+        <v>10/31</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1577,7 +1577,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>10/25</v>
+        <v>11/01</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>10/26</v>
+        <v>11/02</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>10/27</v>
+        <v>11/03</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>10/28</v>
+        <v>11/04</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>10/29</v>
+        <v>11/05</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1647,7 +1647,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>10/30</v>
+        <v>11/06</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1661,7 +1661,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>10/31</v>
+        <v>11/07</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1675,21 +1675,21 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>11/01</v>
+        <v>11/08</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>188.1</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>188.1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>11/02</v>
+        <v>11/09</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>11/03</v>
+        <v>11/10</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>11/04</v>
+        <v>11/11</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>11/05</v>
+        <v>11/12</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>11/06</v>
+        <v>11/13</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>11/07</v>
+        <v>11/14</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1773,21 +1773,21 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>11/08</v>
+        <v>11/15</v>
       </c>
       <c r="B99">
-        <v>188.1</v>
+        <v>0</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>188.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>11/09</v>
+        <v>11/16</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>11/10</v>
+        <v>11/17</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>11/11</v>
+        <v>11/18</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,49 +1829,49 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>11/12</v>
+        <v>11/19</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>11/13</v>
+        <v>11/20</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>288</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>11/14</v>
+        <v>11/21</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>299</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>11/15</v>
+        <v>11/22</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>11/16</v>
+        <v>11/23</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>11/17</v>
+        <v>11/24</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>11/18</v>
+        <v>11/25</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1927,49 +1927,49 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>11/19</v>
+        <v>11/26</v>
       </c>
       <c r="B110">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>11/20</v>
+        <v>11/27</v>
       </c>
       <c r="B111">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>11/21</v>
+        <v>11/28</v>
       </c>
       <c r="B112">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>11/22</v>
+        <v>11/29</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>11/23</v>
+        <v>11/30</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>11/24</v>
+        <v>12/01</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>11/25</v>
+        <v>12/02</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>11/26</v>
+        <v>12/03</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>11/27</v>
+        <v>12/04</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>11/28</v>
+        <v>12/05</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>11/29</v>
+        <v>12/06</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>11/30</v>
+        <v>12/07</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>12/01</v>
+        <v>12/08</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>12/02</v>
+        <v>12/09</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>12/03</v>
+        <v>12/10</v>
       </c>
       <c r="B124">
         <v>0</v>

--- a/ok-fc_occupancy_pace_150day.xlsx
+++ b/ok-fc_occupancy_pace_150day.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D124"/>
+  <dimension ref="A1:D138"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,119 +415,119 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>08/10</v>
+        <v>08/17</v>
       </c>
       <c r="B2">
-        <v>236.66666666666666</v>
+        <v>254.5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>710</v>
+        <v>509</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>08/11</v>
+        <v>08/18</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>08/12</v>
+        <v>08/19</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>08/13</v>
+        <v>08/20</v>
       </c>
       <c r="B5">
-        <v>93.5</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>08/14</v>
+        <v>08/21</v>
       </c>
       <c r="B6">
-        <v>290.59090909090907</v>
+        <v>243.464</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>3196.5</v>
+        <v>1217.32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>08/15</v>
+        <v>08/22</v>
       </c>
       <c r="B7">
-        <v>278.3</v>
+        <v>248.04399999999995</v>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>3061.3</v>
+        <v>1240.2199999999998</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>08/16</v>
+        <v>08/23</v>
       </c>
       <c r="B8">
-        <v>199.45666666666668</v>
+        <v>197.1</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>598.37</v>
+        <v>394.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>08/17</v>
+        <v>08/24</v>
       </c>
       <c r="B9">
-        <v>270</v>
+        <v>196.05</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>270</v>
+        <v>392.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>08/18</v>
+        <v>08/25</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -541,7 +541,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>08/19</v>
+        <v>08/26</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -555,301 +555,301 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>08/20</v>
+        <v>08/27</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>08/21</v>
+        <v>08/28</v>
       </c>
       <c r="B13">
-        <v>283.848</v>
+        <v>308</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>1419.24</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>08/22</v>
+        <v>08/29</v>
       </c>
       <c r="B14">
-        <v>290.168</v>
+        <v>325.5</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>1450.8400000000001</v>
+        <v>651</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>08/23</v>
+        <v>08/30</v>
       </c>
       <c r="B15">
-        <v>197.1</v>
+        <v>219.60750000000002</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D15">
-        <v>394.2</v>
+        <v>878.4300000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>08/24</v>
+        <v>08/31</v>
       </c>
       <c r="B16">
-        <v>196.05</v>
+        <v>214.43</v>
       </c>
       <c r="C16">
         <v>2</v>
       </c>
       <c r="D16">
-        <v>392.1</v>
+        <v>428.86</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>08/25</v>
+        <v>09/01</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>08/26</v>
+        <v>09/02</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>08/27</v>
+        <v>09/03</v>
       </c>
       <c r="B19">
-        <v>522</v>
+        <v>226.5</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19">
-        <v>522</v>
+        <v>453</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>08/28</v>
+        <v>09/04</v>
       </c>
       <c r="B20">
-        <v>616</v>
+        <v>317.22222222222223</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D20">
-        <v>616</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>08/29</v>
+        <v>09/05</v>
       </c>
       <c r="B21">
-        <v>325.5</v>
+        <v>311.09090909090907</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D21">
-        <v>651</v>
+        <v>3422</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>08/30</v>
+        <v>09/06</v>
       </c>
       <c r="B22">
-        <v>311.24</v>
+        <v>318.5</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>933.72</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>08/31</v>
+        <v>09/07</v>
       </c>
       <c r="B23">
-        <v>395.72</v>
+        <v>209.9</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23">
-        <v>395.72</v>
+        <v>419.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>09/01</v>
+        <v>09/08</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>213.25</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>426.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>09/02</v>
+        <v>09/09</v>
       </c>
       <c r="B25">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>09/03</v>
+        <v>09/10</v>
       </c>
       <c r="B26">
-        <v>226.5</v>
+        <v>253</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>453</v>
+        <v>253</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>09/04</v>
+        <v>09/11</v>
       </c>
       <c r="B27">
-        <v>355.5</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>2844</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>09/05</v>
+        <v>09/12</v>
       </c>
       <c r="B28">
-        <v>364.5</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>3645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>09/06</v>
+        <v>09/13</v>
       </c>
       <c r="B29">
-        <v>442.75</v>
+        <v>229</v>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>1771</v>
+        <v>229</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>09/07</v>
+        <v>09/14</v>
       </c>
       <c r="B30">
-        <v>209.9</v>
+        <v>194.5</v>
       </c>
       <c r="C30">
         <v>2</v>
       </c>
       <c r="D30">
-        <v>419.8</v>
+        <v>389</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>09/08</v>
+        <v>09/15</v>
       </c>
       <c r="B31">
-        <v>213.25</v>
+        <v>194</v>
       </c>
       <c r="C31">
         <v>2</v>
       </c>
       <c r="D31">
-        <v>426.5</v>
+        <v>388</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>09/09</v>
+        <v>09/16</v>
       </c>
       <c r="B32">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>09/10</v>
+        <v>09/17</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -863,7 +863,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>09/11</v>
+        <v>09/18</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -877,77 +877,77 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>09/12</v>
+        <v>09/19</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>290</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>09/13</v>
+        <v>09/20</v>
       </c>
       <c r="B36">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36">
-        <v>229</v>
+        <v>251</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>09/14</v>
+        <v>09/21</v>
       </c>
       <c r="B37">
-        <v>194.5</v>
+        <v>261</v>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>389</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>09/15</v>
+        <v>09/22</v>
       </c>
       <c r="B38">
-        <v>194</v>
+        <v>259</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38">
-        <v>388</v>
+        <v>259</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>09/16</v>
+        <v>09/23</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>256</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>09/17</v>
+        <v>09/24</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -961,35 +961,35 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>09/18</v>
+        <v>09/25</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>09/19</v>
+        <v>09/26</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>09/20</v>
+        <v>09/27</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1003,49 +1003,49 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>09/21</v>
+        <v>09/28</v>
       </c>
       <c r="B44">
-        <v>261</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>09/22</v>
+        <v>09/29</v>
       </c>
       <c r="B45">
-        <v>259</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>09/23</v>
+        <v>09/30</v>
       </c>
       <c r="B46">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>09/24</v>
+        <v>10/01</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -1059,63 +1059,63 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>09/25</v>
+        <v>10/02</v>
       </c>
       <c r="B48">
-        <v>300</v>
+        <v>299.835</v>
       </c>
       <c r="C48">
         <v>2</v>
       </c>
       <c r="D48">
-        <v>600</v>
+        <v>599.67</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>09/26</v>
+        <v>10/03</v>
       </c>
       <c r="B49">
-        <v>300</v>
+        <v>287.04</v>
       </c>
       <c r="C49">
         <v>2</v>
       </c>
       <c r="D49">
-        <v>600</v>
+        <v>574.08</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>09/27</v>
+        <v>10/04</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>09/28</v>
+        <v>10/05</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>165</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>09/29</v>
+        <v>10/06</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1129,7 +1129,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>09/30</v>
+        <v>10/07</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1143,77 +1143,77 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>10/01</v>
+        <v>10/08</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>302</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>10/02</v>
+        <v>10/09</v>
       </c>
       <c r="B55">
-        <v>299.835</v>
+        <v>306.4</v>
       </c>
       <c r="C55">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D55">
-        <v>599.67</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>10/03</v>
+        <v>10/10</v>
       </c>
       <c r="B56">
-        <v>287.04</v>
+        <v>305</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D56">
-        <v>574.08</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>10/04</v>
+        <v>10/11</v>
       </c>
       <c r="B57">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>10/05</v>
+        <v>10/12</v>
       </c>
       <c r="B58">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>10/06</v>
+        <v>10/13</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1227,7 +1227,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>10/07</v>
+        <v>10/14</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1241,63 +1241,63 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>10/08</v>
+        <v>10/15</v>
       </c>
       <c r="B61">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61">
-        <v>302</v>
+        <v>356</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>10/09</v>
+        <v>10/16</v>
       </c>
       <c r="B62">
-        <v>302.25</v>
+        <v>381.6666666666667</v>
       </c>
       <c r="C62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D62">
-        <v>1209</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>10/10</v>
+        <v>10/17</v>
       </c>
       <c r="B63">
-        <v>298.5</v>
+        <v>363.6666666666667</v>
       </c>
       <c r="C63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D63">
-        <v>1194</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>10/11</v>
+        <v>10/18</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>278</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>10/12</v>
+        <v>10/19</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>10/13</v>
+        <v>10/20</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>10/14</v>
+        <v>10/21</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1339,63 +1339,63 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>10/15</v>
+        <v>10/22</v>
       </c>
       <c r="B68">
-        <v>356</v>
+        <v>269</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D68">
-        <v>356</v>
+        <v>538</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>10/16</v>
+        <v>10/23</v>
       </c>
       <c r="B69">
-        <v>381.6666666666667</v>
+        <v>338</v>
       </c>
       <c r="C69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D69">
-        <v>1145</v>
+        <v>676</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>10/17</v>
+        <v>10/24</v>
       </c>
       <c r="B70">
-        <v>363.6666666666667</v>
+        <v>328</v>
       </c>
       <c r="C70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D70">
-        <v>1091</v>
+        <v>656</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>10/18</v>
+        <v>10/25</v>
       </c>
       <c r="B71">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>10/19</v>
+        <v>10/26</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>10/20</v>
+        <v>10/27</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>10/21</v>
+        <v>10/28</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>10/22</v>
+        <v>10/29</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>10/23</v>
+        <v>10/30</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>10/24</v>
+        <v>10/31</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>10/25</v>
+        <v>11/01</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1493,7 +1493,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>10/26</v>
+        <v>11/02</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1507,7 +1507,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>10/27</v>
+        <v>11/03</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>10/28</v>
+        <v>11/04</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>10/29</v>
+        <v>11/05</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>10/30</v>
+        <v>11/06</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>10/31</v>
+        <v>11/07</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1577,21 +1577,21 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>11/01</v>
+        <v>11/08</v>
       </c>
       <c r="B85">
-        <v>0</v>
+        <v>188.1</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>188.1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>11/02</v>
+        <v>11/09</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>11/03</v>
+        <v>11/10</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>11/04</v>
+        <v>11/11</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1633,7 +1633,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>11/05</v>
+        <v>11/12</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1647,7 +1647,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>11/06</v>
+        <v>11/13</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1661,7 +1661,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>11/07</v>
+        <v>11/14</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1675,21 +1675,21 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>11/08</v>
+        <v>11/15</v>
       </c>
       <c r="B92">
-        <v>188.1</v>
+        <v>0</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>188.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>11/09</v>
+        <v>11/16</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>11/10</v>
+        <v>11/17</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>11/11</v>
+        <v>11/18</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1731,49 +1731,49 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>11/12</v>
+        <v>11/19</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>11/13</v>
+        <v>11/20</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>288</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>11/14</v>
+        <v>11/21</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>299</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>11/15</v>
+        <v>11/22</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>11/16</v>
+        <v>11/23</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>11/17</v>
+        <v>11/24</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>11/18</v>
+        <v>11/25</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,49 +1829,49 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>11/19</v>
+        <v>11/26</v>
       </c>
       <c r="B103">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D103">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>11/20</v>
+        <v>11/27</v>
       </c>
       <c r="B104">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>11/21</v>
+        <v>11/28</v>
       </c>
       <c r="B105">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>11/22</v>
+        <v>11/29</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>11/23</v>
+        <v>11/30</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>11/24</v>
+        <v>12/01</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>11/25</v>
+        <v>12/02</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>11/26</v>
+        <v>12/03</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>11/27</v>
+        <v>12/04</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>11/28</v>
+        <v>12/05</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>11/29</v>
+        <v>12/06</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>11/30</v>
+        <v>12/07</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>12/01</v>
+        <v>12/08</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>12/02</v>
+        <v>12/09</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>12/03</v>
+        <v>12/10</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>12/04</v>
+        <v>12/11</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>12/05</v>
+        <v>12/12</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>12/06</v>
+        <v>12/13</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>12/07</v>
+        <v>12/14</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>12/08</v>
+        <v>12/15</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>12/09</v>
+        <v>12/16</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>12/10</v>
+        <v>12/17</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -2132,12 +2132,208 @@
         <v>0</v>
       </c>
       <c r="D124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>12/18</v>
+      </c>
+      <c r="B125">
+        <v>0</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>12/19</v>
+      </c>
+      <c r="B126">
+        <v>0</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>12/20</v>
+      </c>
+      <c r="B127">
+        <v>0</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>12/21</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>12/22</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>12/23</v>
+      </c>
+      <c r="B130">
+        <v>0</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>12/24</v>
+      </c>
+      <c r="B131">
+        <v>0</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>12/25</v>
+      </c>
+      <c r="B132">
+        <v>0</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>12/26</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>12/27</v>
+      </c>
+      <c r="B134">
+        <v>0</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>12/28</v>
+      </c>
+      <c r="B135">
+        <v>0</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>12/29</v>
+      </c>
+      <c r="B136">
+        <v>0</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
+      <c r="D136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>12/30</v>
+      </c>
+      <c r="B137">
+        <v>0</v>
+      </c>
+      <c r="C137">
+        <v>0</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>12/31</v>
+      </c>
+      <c r="B138">
+        <v>0</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+      <c r="D138">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D124"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D138"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ok-fc_occupancy_pace_150day.xlsx
+++ b/ok-fc_occupancy_pace_150day.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D138"/>
+  <dimension ref="A1:D131"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,357 +415,357 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>08/17</v>
+        <v>08/24</v>
       </c>
       <c r="B2">
-        <v>254.5</v>
+        <v>196.05</v>
       </c>
       <c r="C2">
         <v>2</v>
       </c>
       <c r="D2">
-        <v>509</v>
+        <v>392.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>08/18</v>
+        <v>08/25</v>
       </c>
       <c r="B3">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>08/19</v>
+        <v>08/26</v>
       </c>
       <c r="B4">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>08/20</v>
+        <v>08/27</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>261</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>08/21</v>
+        <v>08/28</v>
       </c>
       <c r="B6">
-        <v>243.464</v>
+        <v>308</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>1217.32</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>08/22</v>
+        <v>08/29</v>
       </c>
       <c r="B7">
-        <v>248.04399999999995</v>
+        <v>325.5</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>1240.2199999999998</v>
+        <v>651</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>08/23</v>
+        <v>08/30</v>
       </c>
       <c r="B8">
-        <v>197.1</v>
+        <v>219.60750000000002</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8">
-        <v>394.2</v>
+        <v>878.4300000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>08/24</v>
+        <v>08/31</v>
       </c>
       <c r="B9">
-        <v>196.05</v>
+        <v>214.43</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9">
-        <v>392.1</v>
+        <v>428.86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>08/25</v>
+        <v>09/01</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>08/26</v>
+        <v>09/02</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>08/27</v>
+        <v>09/03</v>
       </c>
       <c r="B12">
-        <v>261</v>
+        <v>226.5</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12">
-        <v>261</v>
+        <v>453</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>08/28</v>
+        <v>09/04</v>
       </c>
       <c r="B13">
-        <v>308</v>
+        <v>317.22222222222223</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D13">
-        <v>308</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>08/29</v>
+        <v>09/05</v>
       </c>
       <c r="B14">
-        <v>325.5</v>
+        <v>311.09090909090907</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D14">
-        <v>651</v>
+        <v>3422</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>08/30</v>
+        <v>09/06</v>
       </c>
       <c r="B15">
-        <v>219.60750000000002</v>
+        <v>328</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15">
-        <v>878.4300000000001</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>08/31</v>
+        <v>09/07</v>
       </c>
       <c r="B16">
-        <v>214.43</v>
+        <v>232.9333333333333</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16">
-        <v>428.86</v>
+        <v>698.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>09/01</v>
+        <v>09/08</v>
       </c>
       <c r="B17">
-        <v>229</v>
+        <v>213.25</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>229</v>
+        <v>426.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>09/02</v>
+        <v>09/09</v>
       </c>
       <c r="B18">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>09/03</v>
+        <v>09/10</v>
       </c>
       <c r="B19">
-        <v>226.5</v>
+        <v>253</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>453</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>09/04</v>
+        <v>09/11</v>
       </c>
       <c r="B20">
-        <v>317.22222222222223</v>
+        <v>257.6</v>
       </c>
       <c r="C20">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>2855</v>
+        <v>515.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>09/05</v>
+        <v>09/12</v>
       </c>
       <c r="B21">
-        <v>311.09090909090907</v>
+        <v>259.2</v>
       </c>
       <c r="C21">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>3422</v>
+        <v>518.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>09/06</v>
+        <v>09/13</v>
       </c>
       <c r="B22">
-        <v>318.5</v>
+        <v>229</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D22">
-        <v>1274</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>09/07</v>
+        <v>09/14</v>
       </c>
       <c r="B23">
-        <v>209.9</v>
+        <v>194.5</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
       <c r="D23">
-        <v>419.8</v>
+        <v>389</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>09/08</v>
+        <v>09/15</v>
       </c>
       <c r="B24">
-        <v>213.25</v>
+        <v>194</v>
       </c>
       <c r="C24">
         <v>2</v>
       </c>
       <c r="D24">
-        <v>426.5</v>
+        <v>388</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>09/09</v>
+        <v>09/16</v>
       </c>
       <c r="B25">
-        <v>217</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>09/10</v>
+        <v>09/17</v>
       </c>
       <c r="B26">
-        <v>253</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>09/11</v>
+        <v>09/18</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -779,7 +779,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>09/12</v>
+        <v>09/19</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -793,63 +793,63 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>09/13</v>
+        <v>09/20</v>
       </c>
       <c r="B29">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>09/14</v>
+        <v>09/21</v>
       </c>
       <c r="B30">
-        <v>194.5</v>
+        <v>261</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>389</v>
+        <v>261</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>09/15</v>
+        <v>09/22</v>
       </c>
       <c r="B31">
-        <v>194</v>
+        <v>259</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31">
-        <v>388</v>
+        <v>259</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>09/16</v>
+        <v>09/23</v>
       </c>
       <c r="B32">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>09/17</v>
+        <v>09/24</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -863,91 +863,91 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>09/18</v>
+        <v>09/25</v>
       </c>
       <c r="B34">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>600</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>09/19</v>
+        <v>09/26</v>
       </c>
       <c r="B35">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35">
-        <v>290</v>
+        <v>600</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>09/20</v>
+        <v>09/27</v>
       </c>
       <c r="B36">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>251</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>09/21</v>
+        <v>09/28</v>
       </c>
       <c r="B37">
-        <v>261</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>261</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>09/22</v>
+        <v>09/29</v>
       </c>
       <c r="B38">
-        <v>259</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>09/23</v>
+        <v>09/30</v>
       </c>
       <c r="B39">
-        <v>256</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>256</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>09/24</v>
+        <v>10/01</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -961,63 +961,63 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>09/25</v>
+        <v>10/02</v>
       </c>
       <c r="B41">
-        <v>300</v>
+        <v>327.89</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D41">
-        <v>600</v>
+        <v>983.67</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>09/26</v>
+        <v>10/03</v>
       </c>
       <c r="B42">
-        <v>300</v>
+        <v>313.0266666666667</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42">
-        <v>600</v>
+        <v>939.08</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>09/27</v>
+        <v>10/04</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>09/28</v>
+        <v>10/05</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>09/29</v>
+        <v>10/06</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -1031,7 +1031,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>09/30</v>
+        <v>10/07</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -1045,77 +1045,77 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>10/01</v>
+        <v>10/08</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>302</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>10/02</v>
+        <v>10/09</v>
       </c>
       <c r="B48">
-        <v>299.835</v>
+        <v>307</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D48">
-        <v>599.67</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>10/03</v>
+        <v>10/10</v>
       </c>
       <c r="B49">
-        <v>287.04</v>
+        <v>306.85714285714283</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D49">
-        <v>574.08</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>10/04</v>
+        <v>10/11</v>
       </c>
       <c r="B50">
-        <v>180</v>
+        <v>304.5</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50">
-        <v>180</v>
+        <v>609</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>10/05</v>
+        <v>10/12</v>
       </c>
       <c r="B51">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>10/06</v>
+        <v>10/13</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -1129,7 +1129,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>10/07</v>
+        <v>10/14</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -1143,63 +1143,63 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>10/08</v>
+        <v>10/15</v>
       </c>
       <c r="B54">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="C54">
         <v>1</v>
       </c>
       <c r="D54">
-        <v>302</v>
+        <v>356</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>10/09</v>
+        <v>10/16</v>
       </c>
       <c r="B55">
-        <v>306.4</v>
+        <v>393.5</v>
       </c>
       <c r="C55">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D55">
-        <v>1532</v>
+        <v>787</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>10/10</v>
+        <v>10/17</v>
       </c>
       <c r="B56">
-        <v>305</v>
+        <v>366.5</v>
       </c>
       <c r="C56">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D56">
-        <v>1525</v>
+        <v>733</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>10/11</v>
+        <v>10/18</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>278</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>10/12</v>
+        <v>10/19</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -1213,7 +1213,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>10/13</v>
+        <v>10/20</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -1227,7 +1227,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>10/14</v>
+        <v>10/21</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -1241,63 +1241,63 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>10/15</v>
+        <v>10/22</v>
       </c>
       <c r="B61">
-        <v>356</v>
+        <v>269</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61">
-        <v>356</v>
+        <v>538</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>10/16</v>
+        <v>10/23</v>
       </c>
       <c r="B62">
-        <v>381.6666666666667</v>
+        <v>338</v>
       </c>
       <c r="C62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D62">
-        <v>1145</v>
+        <v>676</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>10/17</v>
+        <v>10/24</v>
       </c>
       <c r="B63">
-        <v>363.6666666666667</v>
+        <v>328</v>
       </c>
       <c r="C63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D63">
-        <v>1091</v>
+        <v>656</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>10/18</v>
+        <v>10/25</v>
       </c>
       <c r="B64">
-        <v>278</v>
+        <v>0</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>278</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>10/19</v>
+        <v>10/26</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>10/20</v>
+        <v>10/27</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -1325,7 +1325,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>10/21</v>
+        <v>10/28</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -1339,49 +1339,49 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>10/22</v>
+        <v>10/29</v>
       </c>
       <c r="B68">
-        <v>269</v>
+        <v>0</v>
       </c>
       <c r="C68">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>538</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>10/23</v>
+        <v>10/30</v>
       </c>
       <c r="B69">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="C69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D69">
-        <v>676</v>
+        <v>316</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>10/24</v>
+        <v>10/31</v>
       </c>
       <c r="B70">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D70">
-        <v>656</v>
+        <v>311</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>10/25</v>
+        <v>11/01</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>10/26</v>
+        <v>11/02</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -1409,7 +1409,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>10/27</v>
+        <v>11/03</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>10/28</v>
+        <v>11/04</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>10/29</v>
+        <v>11/05</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>10/30</v>
+        <v>11/06</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>10/31</v>
+        <v>11/07</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1479,21 +1479,21 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>11/01</v>
+        <v>11/08</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>188.1</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>188.1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>11/02</v>
+        <v>11/09</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1507,7 +1507,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>11/03</v>
+        <v>11/10</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>11/04</v>
+        <v>11/11</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -1535,7 +1535,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>11/05</v>
+        <v>11/12</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>11/06</v>
+        <v>11/13</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>11/07</v>
+        <v>11/14</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1577,21 +1577,21 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>11/08</v>
+        <v>11/15</v>
       </c>
       <c r="B85">
-        <v>188.1</v>
+        <v>0</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>188.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>11/09</v>
+        <v>11/16</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>11/10</v>
+        <v>11/17</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>11/11</v>
+        <v>11/18</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -1633,49 +1633,49 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>11/12</v>
+        <v>11/19</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>11/13</v>
+        <v>11/20</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>288</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>11/14</v>
+        <v>11/21</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>299</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>11/15</v>
+        <v>11/22</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1689,7 +1689,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>11/16</v>
+        <v>11/23</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>11/17</v>
+        <v>11/24</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1717,7 +1717,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>11/18</v>
+        <v>11/25</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1731,49 +1731,49 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>11/19</v>
+        <v>11/26</v>
       </c>
       <c r="B96">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96">
-        <v>250</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>11/20</v>
+        <v>11/27</v>
       </c>
       <c r="B97">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>288</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>11/21</v>
+        <v>11/28</v>
       </c>
       <c r="B98">
-        <v>299</v>
+        <v>0</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98">
-        <v>299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>11/22</v>
+        <v>11/29</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>11/23</v>
+        <v>11/30</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>11/24</v>
+        <v>12/01</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -1815,7 +1815,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>11/25</v>
+        <v>12/02</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -1829,7 +1829,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>11/26</v>
+        <v>12/03</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>11/27</v>
+        <v>12/04</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>11/28</v>
+        <v>12/05</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1871,7 +1871,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>11/29</v>
+        <v>12/06</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>11/30</v>
+        <v>12/07</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>12/01</v>
+        <v>12/08</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>12/02</v>
+        <v>12/09</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -1927,7 +1927,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>12/03</v>
+        <v>12/10</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -1941,7 +1941,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>12/04</v>
+        <v>12/11</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -1955,7 +1955,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>12/05</v>
+        <v>12/12</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>12/06</v>
+        <v>12/13</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>12/07</v>
+        <v>12/14</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>12/08</v>
+        <v>12/15</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>12/09</v>
+        <v>12/16</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>12/10</v>
+        <v>12/17</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>12/11</v>
+        <v>12/18</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>12/12</v>
+        <v>12/19</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -2067,7 +2067,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>12/13</v>
+        <v>12/20</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>12/14</v>
+        <v>12/21</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -2095,7 +2095,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>12/15</v>
+        <v>12/22</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>12/16</v>
+        <v>12/23</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>12/17</v>
+        <v>12/24</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>12/18</v>
+        <v>12/25</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -2151,7 +2151,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>12/19</v>
+        <v>12/26</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -2165,7 +2165,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>12/20</v>
+        <v>12/27</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>12/21</v>
+        <v>12/28</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>12/22</v>
+        <v>12/29</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -2207,7 +2207,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>12/23</v>
+        <v>12/30</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -2221,7 +2221,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>12/24</v>
+        <v>12/31</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -2230,110 +2230,12 @@
         <v>0</v>
       </c>
       <c r="D131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="str">
-        <v>12/25</v>
-      </c>
-      <c r="B132">
-        <v>0</v>
-      </c>
-      <c r="C132">
-        <v>0</v>
-      </c>
-      <c r="D132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>12/26</v>
-      </c>
-      <c r="B133">
-        <v>0</v>
-      </c>
-      <c r="C133">
-        <v>0</v>
-      </c>
-      <c r="D133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="str">
-        <v>12/27</v>
-      </c>
-      <c r="B134">
-        <v>0</v>
-      </c>
-      <c r="C134">
-        <v>0</v>
-      </c>
-      <c r="D134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v>12/28</v>
-      </c>
-      <c r="B135">
-        <v>0</v>
-      </c>
-      <c r="C135">
-        <v>0</v>
-      </c>
-      <c r="D135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="str">
-        <v>12/29</v>
-      </c>
-      <c r="B136">
-        <v>0</v>
-      </c>
-      <c r="C136">
-        <v>0</v>
-      </c>
-      <c r="D136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v>12/30</v>
-      </c>
-      <c r="B137">
-        <v>0</v>
-      </c>
-      <c r="C137">
-        <v>0</v>
-      </c>
-      <c r="D137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>12/31</v>
-      </c>
-      <c r="B138">
-        <v>0</v>
-      </c>
-      <c r="C138">
-        <v>0</v>
-      </c>
-      <c r="D138">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D138"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D131"/>
   </ignoredErrors>
 </worksheet>
 </file>